--- a/workspaces/btc_daily_14days/rsi/rsi_18.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_18.xlsx
@@ -572,49 +572,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.618438320209975</v>
+        <v>-5.784324240972666</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.231813702050196</v>
+        <v>-7.449014033931803</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>4.877504671447412</v>
+        <v>5.02127738156954</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.00905012997692</v>
+        <v>5.156827871866277</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.72750377661578</v>
+        <v>11.04552545571798</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.02787264136569</v>
+        <v>11.35285725128959</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.572876363892327</v>
+        <v>-1.623825378247247</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.30194395307786</v>
+        <v>-8.550274534676468</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.0281011255178</v>
+        <v>1.052586194702478</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1762965350737176</v>
+        <v>0.1755666394879043</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.10349788746835</v>
+        <v>3.186678487456668</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.53610693018945</v>
+        <v>12.89927183230627</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.498382664031574</v>
+        <v>4.626048830945741</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.523000405586117</v>
+        <v>-1.575842740003772</v>
       </c>
     </row>
     <row r="7">
@@ -624,49 +624,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-9.311620138392826</v>
+        <v>-9.506976800330115</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-10.92595018530015</v>
+        <v>-11.15781115214082</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-13.59756685639041</v>
+        <v>-13.88260015519614</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-13.4706041546594</v>
+        <v>-13.75288595447601</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-9.462875894373788</v>
+        <v>-9.659973514797997</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-6.891926537546972</v>
+        <v>-7.036480031712294</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-11.53099499675659</v>
+        <v>-11.77595108947328</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-12.00185272999961</v>
+        <v>-12.25596814419869</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-18.89795474949027</v>
+        <v>-19.29821498053579</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-24.31043935531156</v>
+        <v>-24.82422347311536</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-20.94964570327809</v>
+        <v>-21.39468136586992</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-23.19512756376766</v>
+        <v>-23.68587960387121</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-23.60777260993977</v>
+        <v>-24.10613421481823</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-21.08325930300965</v>
+        <v>-21.5308314871931</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>59</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11.91334134080697</v>
+        <v>11.88647622066861</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.953787387736313</v>
+        <v>-4.941926940743862</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.216063802999578</v>
+        <v>8.197703641039716</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.956057354078659</v>
+        <v>4.945104465267981</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.418411175519921</v>
+        <v>4.408452676757257</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.020229889279314</v>
+        <v>3.01353743576319</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.854161490927787</v>
+        <v>-3.844743566546306</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.927327760386774</v>
+        <v>-0.9246380520084614</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.105994291934891</v>
+        <v>4.097574589000473</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.540404037946018</v>
+        <v>-3.531276090427902</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.745727134695827</v>
+        <v>-3.736029414743953</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.409955026673913</v>
+        <v>-5.396561511637344</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.13228231521564</v>
+        <v>-4.121900868344952</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.4845981801302131</v>
+        <v>-0.4823490275940969</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-11.92740058436092</v>
+        <v>-12.1335204889635</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.162524536977642</v>
+        <v>-3.223293819077405</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.50223599714311</v>
+        <v>-4.580981935442097</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.205490128243795</v>
+        <v>-7.331953562610842</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.079999363770604</v>
+        <v>-2.115760990473348</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.043748219483511</v>
+        <v>-5.132019692435669</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.549760251153707</v>
+        <v>-5.652194729217094</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-11.67928881314828</v>
+        <v>-11.88696199605688</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-12.68582875122157</v>
+        <v>-12.9123781803171</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-15.41202067237974</v>
+        <v>-15.68903358716889</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-14.66732898767643</v>
+        <v>-14.93224844994757</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-16.52404275263531</v>
+        <v>-16.82094221567863</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-14.10288953272914</v>
+        <v>-14.35658144200814</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.131487191375889</v>
+        <v>-9.299167802039989</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.028300810224806</v>
+        <v>4.055237350062377</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1921353784398008</v>
+        <v>-0.1965910652071798</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.19732849223719</v>
+        <v>-3.221294500298399</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.197699836077426</v>
+        <v>-2.215365006221916</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.9961098022714054</v>
+        <v>-1.003480791077436</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-8.532982227403359</v>
+        <v>-8.595256719391145</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-5.136170518629726</v>
+        <v>-5.176526358489859</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.347082919506825</v>
+        <v>-7.403917486714676</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-9.152420421936725</v>
+        <v>-9.222948428526649</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-7.765579454672931</v>
+        <v>-7.828034936696518</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-7.097704094202967</v>
+        <v>-7.155595278557563</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.321390721391218</v>
+        <v>-5.366826156300242</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-9.223472502424215</v>
+        <v>-9.295852697068916</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.008618094811141</v>
+        <v>-2.028587505143896</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.870902765061523</v>
+        <v>4.979392349459751</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>7.912562524418625</v>
+        <v>8.083878504014038</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.744029033747204</v>
+        <v>6.892940892017442</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.65195551783362</v>
+        <v>7.819614588244846</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.212316300640374</v>
+        <v>5.330450896795178</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.286154995785985</v>
+        <v>6.42026663573413</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7.755329080457528</v>
+        <v>7.917726536054161</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.951218297128491</v>
+        <v>7.091376228863226</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>8.105749249867898</v>
+        <v>8.268539705307575</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>8.83138924539459</v>
+        <v>9.005716107581591</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>8.631453111632581</v>
+        <v>8.800962783263657</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.561273515785224</v>
+        <v>5.660742766005917</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>9.805088820462508</v>
+        <v>10.00239291696541</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.386525195380173</v>
+        <v>5.490209487337658</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>156</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.057540884312829</v>
+        <v>-5.05316131854584</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-7.31231397684634</v>
+        <v>-7.305792461214772</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.219711663268384</v>
+        <v>-3.216888204945484</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.042329769123782</v>
+        <v>2.040628903092944</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.069953813479167</v>
+        <v>4.066310252123628</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.292098976270445</v>
+        <v>6.28682911291606</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.923955702415022</v>
+        <v>4.920044113592503</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.739359640618758</v>
+        <v>5.73491199686228</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.470271155706726</v>
+        <v>2.468783905551774</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.9776431557190364</v>
+        <v>0.9776330794982115</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.98061568619071</v>
+        <v>3.978007960308688</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.014950477677424</v>
+        <v>4.012391117654268</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.236062084012914</v>
+        <v>4.233162147735001</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.278251024934796</v>
+        <v>1.277755274882793</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>179</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.696505813868363</v>
+        <v>1.695135919383617</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6436285642165913</v>
+        <v>0.6435171279099166</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.428234101457079</v>
+        <v>-1.426765361441781</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.212398917302217</v>
+        <v>-5.207616333978969</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.955171554795712</v>
+        <v>-2.952741459665788</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.421013445711516</v>
+        <v>-0.4206626504417486</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.624411877994127</v>
+        <v>-1.622714803468213</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.7036800129281673</v>
+        <v>0.7033978871357576</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.4759845882642182</v>
+        <v>-0.4749204348006089</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.886322023646223</v>
+        <v>-1.883704837705622</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.209500092197274</v>
+        <v>-3.205776597777522</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9384807537421338</v>
+        <v>-0.9367565689235846</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.477293426018633</v>
+        <v>-2.474329615622672</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.345623550100555</v>
+        <v>-3.341926719100577</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>192</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.71489501312336</v>
+        <v>2.712367043093785</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.501500791985023</v>
+        <v>-1.499534215552416</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.460632218131316</v>
+        <v>-3.45700485059028</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.374169482787131</v>
+        <v>-4.369627507163322</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.827313827259324</v>
+        <v>-2.824715388902277</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.07698566111898941</v>
+        <v>0.07689321548028971</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.555858490128394</v>
+        <v>1.55465949820789</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.039882665052637</v>
+        <v>-2.037523900573611</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.622642519809105</v>
+        <v>-2.619357120089248</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.516646219007903</v>
+        <v>-4.51114897178384</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.5508159207068175</v>
+        <v>-0.5492356294347545</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.03771462923833</v>
+        <v>-1.035685805422652</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.9369264256548391</v>
+        <v>-0.9351070830342252</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.81498593289502</v>
+        <v>-3.810385750757938</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.766165592937249</v>
+        <v>-4.78989659053785</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.969893145186703</v>
+        <v>-2.988025250962778</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-7.346193510610753</v>
+        <v>-7.385548467877783</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.92349005805832</v>
+        <v>-2.941056078591764</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.167795201121287</v>
+        <v>-5.193763007949649</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.303404654073525</v>
+        <v>-4.324892498805539</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.66064586995941</v>
+        <v>-6.695340501791982</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.418369914947675</v>
+        <v>-5.448238186287767</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.045505813688848</v>
+        <v>-6.080666643898766</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.614509974305982</v>
+        <v>-4.645077543212416</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.25117705380908</v>
+        <v>-4.278402296101419</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.079808810060563</v>
+        <v>-3.101161995898842</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.77289595832886</v>
+        <v>-5.807130892558163</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.660809789873987</v>
+        <v>-6.700266703138887</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>188</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.6849276819121</v>
+        <v>-5.680554719365382</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.446287738973091</v>
+        <v>-1.444587191205038</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2868516185624514</v>
+        <v>0.2873534027823652</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.546563006165059</v>
+        <v>2.545266109857835</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.475783589323619</v>
+        <v>1.474930001168758</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.420338381453675</v>
+        <v>-1.419117422817706</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.231604959028765</v>
+        <v>-5.227255395409252</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-4.102375398379699</v>
+        <v>-4.098694113339569</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.631475145323037</v>
+        <v>-3.627779105904729</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.950260045316035</v>
+        <v>-3.945989397315628</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-5.751833495757687</v>
+        <v>-5.746487402484391</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.652759382792226</v>
+        <v>-4.648274457904925</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.008730204810632</v>
+        <v>-4.004699281615665</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.758983424616069</v>
+        <v>-3.754977949339498</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.152206092721826</v>
+        <v>-4.173180374248879</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.240615422209494</v>
+        <v>-6.272275593800757</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-6.372432319597515</v>
+        <v>-6.404642544532727</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-8.614876739823337</v>
+        <v>-8.6553417928775</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.885709212789834</v>
+        <v>-4.908048722235492</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-6.01143741518672</v>
+        <v>-6.039178213091262</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.670278614851284</v>
+        <v>-4.695340501791996</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.608862783087638</v>
+        <v>-5.638714376764199</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.770967983680862</v>
+        <v>-3.794952358184588</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.141044847211006</v>
+        <v>-4.168887067022041</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.242450899180014</v>
+        <v>-6.278402296101419</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-8.579484175846765</v>
+        <v>-8.624971519708375</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-9.472100395362091</v>
+        <v>-9.521416606843751</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-8.748416055988663</v>
+        <v>-8.795504798376989</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.232568754992585</v>
+        <v>-4.255696635828258</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.05036939255624873</v>
+        <v>0.04345968254629895</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.9615869471074134</v>
+        <v>0.9586346440719709</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.953028929203171</v>
+        <v>-1.967880782272495</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.057710596616225</v>
+        <v>-2.069620774637336</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.064964171999605</v>
+        <v>-3.082222505043852</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.40726442787382</v>
+        <v>-1.420231331486434</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.610449078328514</v>
+        <v>-3.634139621097631</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.365188859857227</v>
+        <v>-2.385095839157657</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.6003600264923179</v>
+        <v>-0.6151336879410465</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.543722255074279</v>
+        <v>-2.566611903088315</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.204991271641902</v>
+        <v>-1.222185077620622</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.057942369209577</v>
+        <v>-2.079120911272938</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.80856872394547</v>
+        <v>-1.82939957899665</v>
       </c>
     </row>
     <row r="19">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 21.4</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4078~4089</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4078</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.03562467384167434</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 23.66</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4047~4057</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4047</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.008410336432859822</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 25.92</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4004~4013</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4004</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.1105985599295707</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 28.19</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3945~3954</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3945</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.06551722764548629</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 30.45</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3841~3848</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3841</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.2612394344677824</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 32.71</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3727~3733</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3727</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.145190128758685</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 34.98</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3601~3604</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3601</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.02395996282929502</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 37.24</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3445~3448</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3445</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.2037774570522117</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 39.5</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3266~3269</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3266</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.1220404194657689</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 41.77</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3074~3077</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3074</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.03974966242641642</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 44.03</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2899~2901</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2899</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.2469960127786521</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 46.29</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2711~2713</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2711</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.6580544921748412</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 48.55</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2501~2502</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2501</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.06371595636876</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 50.82</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2272~2272</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2272</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.599871538944953</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 53.08</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2046~2046</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2046</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.514381816642413</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 55.34</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1835~1835</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1835</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.947978573523002</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 57.61</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1650~1650</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1650</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.779288952517298</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 59.87</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1467~1467</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1467</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>2.857618257840464</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 62.13</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1286~1286</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1286</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>3.416359502496093</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 64.4</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1120~1120</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1120</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>3.667275965504309</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 66.66</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>969~969</t>
-        </is>
+      <c r="B26" t="n">
+        <v>969</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>3.234115859356585</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 68.92</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>828~828</t>
-        </is>
+      <c r="B27" t="n">
+        <v>828</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>4.269846703944609</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 71.18</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>678~678</t>
-        </is>
+      <c r="B28" t="n">
+        <v>678</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>4.291222446751675</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 73.45</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>565~565</t>
-        </is>
+      <c r="B29" t="n">
+        <v>565</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>5.38266787448029</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 75.71</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>454~454</t>
-        </is>
+      <c r="B30" t="n">
+        <v>454</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>4.77528414675038</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 77.97</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>351~351</t>
-        </is>
+      <c r="B31" t="n">
+        <v>351</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>5.056419229647574</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 80.24</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>276~276</t>
-        </is>
+      <c r="B32" t="n">
+        <v>276</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>4.390619650804517</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 82.5</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>214~214</t>
-        </is>
+      <c r="B33" t="n">
+        <v>214</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>6.385066352687218</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 84.76</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>141~141</t>
-        </is>
+      <c r="B34" t="n">
+        <v>141</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>5.662590048584349</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 87.03</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.077990251218594</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 21.4</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>82~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>82</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>2.268466441694791</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 23.66</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>113~116</t>
-        </is>
+      <c r="B7" t="n">
+        <v>113</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.09276857634174718</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 25.92</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>156~160</t>
-        </is>
+      <c r="B8" t="n">
+        <v>156</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 28.19</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>215~219</t>
-        </is>
+      <c r="B9" t="n">
+        <v>215</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1.387840218602804</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 30.45</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>319~325</t>
-        </is>
+      <c r="B10" t="n">
+        <v>319</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-2.954976781748435</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 32.71</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>433~440</t>
-        </is>
+      <c r="B11" t="n">
+        <v>433</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-1.129801956573608</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 34.98</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>559~569</t>
-        </is>
+      <c r="B12" t="n">
+        <v>559</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.2306390084367678</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 37.24</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>715~725</t>
-        </is>
+      <c r="B13" t="n">
+        <v>715</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.9072314236582528</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 39.5</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>894~904</t>
-        </is>
+      <c r="B14" t="n">
+        <v>894</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.3916684087055486</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 41.77</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1086~1096</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1086</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.152547081249871</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 44.03</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1261~1272</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1261</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.528029515178531</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 46.29</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1449~1460</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1449</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-1.192068457196271</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 48.55</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1659~1671</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1659</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.565850049713269</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 50.82</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1888~1901</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1888</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.888493554297298</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 53.08</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2114~2127</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2114</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.435610393552714</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 55.34</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2325~2338</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2325</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.509691528079948</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 57.61</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2510~2523</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2510</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.799819612322544</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 59.87</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2693~2706</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2693</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.532610530113892</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 62.13</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2874~2887</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2874</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.506254392257077</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 64.4</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3040~3053</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3040</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.330647622535551</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 66.66</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3191~3204</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3191</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.9640999931188432</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 68.92</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3332~3345</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3332</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.043513058625521</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 71.18</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3482~3495</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3482</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.8196185777207035</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 73.45</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3595~3608</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3595</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.8304671450436842</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 75.71</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3706~3719</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3706</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.5708784922992436</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 77.97</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3809~3822</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3809</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.4526219936793581</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 80.24</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3884~3897</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3884</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.2994429391476245</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 82.5</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3946~3959</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3946</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.3338020484241753</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 84.76</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4019~4032</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4019</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.1868907011623619</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 87.03</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4076~4089</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4076</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.0111688166638757</v>

--- a/workspaces/btc_daily_14days/rsi/rsi_18.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_18.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-18 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-18 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>31</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.784324240972666</v>
+        <v>-5.770007468349988</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.449014033931803</v>
+        <v>-7.433855185016498</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.02127738156954</v>
+        <v>5.03345591917985</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.156827871866277</v>
+        <v>5.168946390186967</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.04552545571798</v>
+        <v>11.05632745542903</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.35285725128959</v>
+        <v>11.36353291525093</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.623825378247247</v>
+        <v>-1.609907349165908</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.550274534676468</v>
+        <v>-8.534546695688348</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.052586194702478</v>
+        <v>1.066003057579394</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1755666394879043</v>
+        <v>0.1894158022943202</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.186678487456668</v>
+        <v>3.199867506829655</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.89927183230627</v>
+        <v>12.91272412102638</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.626048830945741</v>
+        <v>2.805663920863886</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.575842740003772</v>
+        <v>-1.586272375701924</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>43</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-9.506976800330115</v>
+        <v>-9.491816061681064</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-11.15781115214082</v>
+        <v>-11.14180689083636</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-13.88260015519614</v>
+        <v>-13.86584749872574</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-13.75288595447601</v>
+        <v>-13.73619105742281</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-9.659973514797997</v>
+        <v>-9.644174725910595</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-7.036480031712294</v>
+        <v>-7.021384687653352</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-11.77595108947328</v>
+        <v>-11.75960698989015</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-12.25596814419869</v>
+        <v>-12.23939127498639</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-19.29821498053579</v>
+        <v>-19.27983834890819</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-24.82422347311536</v>
+        <v>-24.80425016848148</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-21.39468136586992</v>
+        <v>-22.69625762303866</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-23.68587960387121</v>
+        <v>-23.6724273151511</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-24.10613421481823</v>
+        <v>-24.09257816846662</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-21.5308314871931</v>
+        <v>-21.54126112289126</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>59</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11.88647622066861</v>
+        <v>11.8959879088087</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.941926940743862</v>
+        <v>-4.927733137442928</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.197703641039716</v>
+        <v>8.20864731596803</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.945104465267981</v>
+        <v>4.956844702394193</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.408452676757257</v>
+        <v>4.420437851305472</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.01353743576319</v>
+        <v>3.025820399080992</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.844743566546306</v>
+        <v>-3.830645830569821</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.9246380520084614</v>
+        <v>-0.9111689224507202</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.097574589000473</v>
+        <v>4.109831242821116</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.531276090427902</v>
+        <v>-3.516860581262847</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.736029414743953</v>
+        <v>-3.722572121033735</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.396561511637344</v>
+        <v>-5.383109222917234</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.121900868344952</v>
+        <v>-4.108344821993349</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.4823490275940969</v>
+        <v>-0.4927786632922491</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>104</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-12.1335204889635</v>
+        <v>-12.11763599556065</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.223293819077405</v>
+        <v>-3.209220140637477</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.580981935442097</v>
+        <v>-4.56653300071973</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.331953562610842</v>
+        <v>-7.316802575589278</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.115760990473348</v>
+        <v>-2.101853219481697</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.132019692435669</v>
+        <v>-5.643761151097735</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.652194729217094</v>
+        <v>-6.16782823926664</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-11.88696199605688</v>
+        <v>-11.8706288478886</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-12.9123781803171</v>
+        <v>-12.89573526761204</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-15.68903358716889</v>
+        <v>-15.67141077720151</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-14.93224844994757</v>
+        <v>-14.91879115623735</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-16.82094221567863</v>
+        <v>-16.80748992695852</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-14.35658144200814</v>
+        <v>-14.34302539565654</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.299167802039989</v>
+        <v>-9.309597437738141</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>114</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.055237350062377</v>
+        <v>4.066837880765448</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1965910652071798</v>
+        <v>-0.183411797006066</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.221294500298399</v>
+        <v>-3.207277445729687</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.215365006221916</v>
+        <v>-2.201609721138006</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.003480791077436</v>
+        <v>-0.9899778968601467</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-8.595256719391145</v>
+        <v>-8.582213823096779</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-5.176526358489859</v>
+        <v>-5.163460104189383</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.403917486714676</v>
+        <v>-7.388470354194745</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-9.222948428526649</v>
+        <v>-9.206961298637395</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-7.828034936696518</v>
+        <v>-8.314871824806517</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-7.155595278557563</v>
+        <v>-7.142137984847345</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.366826156300242</v>
+        <v>-5.353373867580132</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-9.295852697068916</v>
+        <v>-9.282296650717313</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.028587505143896</v>
+        <v>-2.039017140842049</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>126</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.979392349459751</v>
+        <v>4.990893299087872</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.083878504014038</v>
+        <v>8.09500570192391</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.892940892017442</v>
+        <v>6.904447400592503</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.819614588244846</v>
+        <v>7.830864696101514</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.330450896795178</v>
+        <v>4.907606871279711</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.42026663573413</v>
+        <v>6.433309532028495</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7.917726536054161</v>
+        <v>7.930792790354637</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>7.091376228863226</v>
+        <v>6.660283077639406</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>8.268539705307575</v>
+        <v>7.835522761995122</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>9.005716107581591</v>
+        <v>9.019121235234422</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>8.800962783263657</v>
+        <v>8.814420076973875</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.660742766005917</v>
+        <v>5.674195054726027</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>10.00239291696541</v>
+        <v>10.01594896331702</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.490209487337658</v>
+        <v>5.479779851639506</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>156</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.05316131854584</v>
+        <v>-5.039197746528679</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-7.305792461214772</v>
+        <v>-7.290723810595267</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.216888204945484</v>
+        <v>-3.202949247384126</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.040628903092944</v>
+        <v>2.053036867391967</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.066310252123628</v>
+        <v>4.079421056498568</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.28682911291606</v>
+        <v>6.299872009210425</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.920044113592503</v>
+        <v>4.933110367892979</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.73491199686228</v>
+        <v>5.748093006157518</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.468783905551774</v>
+        <v>2.481982644506537</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.9776330794982115</v>
+        <v>0.9910382071510426</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.978007960308688</v>
+        <v>3.991465254018905</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.012391117654268</v>
+        <v>4.025843406374378</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.233162147735001</v>
+        <v>4.246718194086604</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.277755274882793</v>
+        <v>1.267325639184641</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>179</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.695135919383617</v>
+        <v>1.707183446246319</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6435171279099166</v>
+        <v>0.6563752866847139</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.426765361441781</v>
+        <v>-1.413278656354571</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.207616333978969</v>
+        <v>-5.193048314408017</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.952741459665788</v>
+        <v>-2.939630655290848</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.4206626504417486</v>
+        <v>-0.4076197541473832</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.622714803468213</v>
+        <v>-1.609648549167737</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.7033978871357576</v>
+        <v>0.7165788964309954</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.4749204348006089</v>
+        <v>-0.4617216958458457</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.883704837705622</v>
+        <v>-1.870299710052791</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.205776597777522</v>
+        <v>-3.192319304067304</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9367565689235846</v>
+        <v>-0.9233042802034745</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.474329615622672</v>
+        <v>-2.460773569271069</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.341926719100577</v>
+        <v>-3.352356354798729</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>192</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.712367043093785</v>
+        <v>2.724026861012931</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.499534215552416</v>
+        <v>-1.48598581014285</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.45700485059028</v>
+        <v>-3.442800277713978</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.355140305607009</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.824715388902277</v>
+        <v>-2.811604584527338</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.07689321548028971</v>
+        <v>0.0899361117746551</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.55465949820789</v>
+        <v>1.567725752508366</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.037523900573611</v>
+        <v>-2.024342891278373</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.619357120089248</v>
+        <v>-2.606158381134485</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.51114897178384</v>
+        <v>-4.497743844131008</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.5492356294347545</v>
+        <v>-0.5357783357245367</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.035685805422652</v>
+        <v>-1.022233516702542</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.9351070830342252</v>
+        <v>-0.9215510366826223</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.810385750757938</v>
+        <v>-3.82081538645609</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>175</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.78989659053785</v>
+        <v>-4.775657785757019</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.988025250962778</v>
+        <v>-2.973775009633293</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-7.385548467877783</v>
+        <v>-7.369728985686152</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.941056078591764</v>
+        <v>-3.241944532012219</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.193763007949649</v>
+        <v>-5.180652203574709</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.324892498805539</v>
+        <v>-4.311849602511174</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.695340501791982</v>
+        <v>-6.682274247491506</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.448238186287767</v>
+        <v>-5.43505717699253</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.080666643898766</v>
+        <v>-6.067467904944003</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.645077543212416</v>
+        <v>-4.631672415559585</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.278402296101419</v>
+        <v>-4.264945002391201</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.101161995898842</v>
+        <v>-3.087709707178732</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.807130892558163</v>
+        <v>-5.79357484620656</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.700266703138887</v>
+        <v>-6.710696338837039</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>188</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.680554719365382</v>
+        <v>-5.665868454279618</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.444587191205038</v>
+        <v>-1.430841702191962</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.2873534027823652</v>
+        <v>0.300604281183432</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.545266109857835</v>
+        <v>2.558245252256299</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.474930001168758</v>
+        <v>1.488040805543697</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.419117422817706</v>
+        <v>-1.406074526523341</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.227255395409252</v>
+        <v>-5.214189141108776</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-4.098694113339569</v>
+        <v>-4.085513104044331</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.627779105904729</v>
+        <v>-3.614580366949966</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.945989397315628</v>
+        <v>-3.932584269662797</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-5.746487402484391</v>
+        <v>-5.733030108774173</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.648274457904925</v>
+        <v>-4.634822169184815</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.004699281615665</v>
+        <v>-3.991143235264062</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.754977949339498</v>
+        <v>-3.76540758503765</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>210</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.173180374248879</v>
+        <v>-4.158650371881336</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.272275593800757</v>
+        <v>-6.256362465802702</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-6.404642544532727</v>
+        <v>-6.655893033567416</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-8.6553417928775</v>
+        <v>-8.642362650479036</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-6.039178213091262</v>
+        <v>-6.026135316796896</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.695340501791996</v>
+        <v>-4.68227424749152</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.638714376764199</v>
+        <v>-5.625533367468961</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.794952358184588</v>
+        <v>-3.781753619229825</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.168887067022041</v>
+        <v>-4.15548193936921</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-8.624971519708375</v>
+        <v>-8.611519230988264</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-9.521416606843751</v>
+        <v>-9.507860560492148</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-8.795504798376989</v>
+        <v>-8.805934434075141</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>229</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.255696635828258</v>
+        <v>-4.240750102693241</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.04345968254629895</v>
+        <v>-0.1869293186107512</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.9586346440719709</v>
+        <v>0.971641775489573</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.967880782272495</v>
+        <v>-1.954901639874031</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.069620774637336</v>
+        <v>-2.056509970262397</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.082222505043852</v>
+        <v>-3.069179608749486</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.420231331486434</v>
+        <v>-1.407165077185958</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.634139621097631</v>
+        <v>-3.620958611802394</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.385095839157657</v>
+        <v>-2.371897100202894</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.6151336879410465</v>
+        <v>-0.6017285602882154</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.566611903088315</v>
+        <v>-2.553154609378097</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.222185077620622</v>
+        <v>-1.208732788900512</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.079120911272938</v>
+        <v>-2.065564864921335</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.82939957899665</v>
+        <v>-1.839829214694802</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>226</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.373818316958264</v>
+        <v>2.385950892428404</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.417111960631175</v>
+        <v>3.430021770207226</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3673759973972182</v>
+        <v>0.3803831288148203</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.272282374420051</v>
+        <v>-1.259303232021587</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.138137217810709</v>
+        <v>-3.125026413435769</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.070783775670265</v>
+        <v>-1.057740879375899</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2705617407301659</v>
+        <v>-0.2574954864296899</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.5896884888068215</v>
+        <v>0.6028694981020593</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3562671495878718</v>
+        <v>-0.3430684106331086</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.091348086828191</v>
+        <v>-2.07794295917536</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.686199473810085</v>
+        <v>1.699656767520302</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.8356268789430246</v>
+        <v>0.8490791676631346</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.74280589631681</v>
+        <v>1.756361942668413</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.877482980805489</v>
+        <v>2.867053345107337</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>211</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.256471495565584</v>
+        <v>-2.499785396639538</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-9.081315250709778</v>
+        <v>-9.068405441133727</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-7.580449360149863</v>
+        <v>-7.567442228732261</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-9.345930824698755</v>
+        <v>-9.33295168230029</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-8.936484741192842</v>
+        <v>-8.923373936817903</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.795440907742581</v>
+        <v>-5.782398011448215</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-7.301975572882156</v>
+        <v>-7.28890931858168</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-6.347358023796247</v>
+        <v>-6.334177014501009</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.460490611400353</v>
+        <v>-5.447291872445589</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-5.362748497850077</v>
+        <v>-5.349343370197246</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.145700874300367</v>
+        <v>-4.132243580590149</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.637384067665828</v>
+        <v>-3.623931778945717</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.583705029321742</v>
+        <v>-3.570148982970139</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-4.755784644912751</v>
+        <v>-4.766214280610903</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>185</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-5.466411293182887</v>
+        <v>-5.453889003507264</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.672579500741982</v>
+        <v>-1.659669691165931</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.526907666797847</v>
+        <v>-1.513900535380245</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.306048168512419</v>
+        <v>1.319027310910883</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.475616289802872</v>
+        <v>-2.462505485427933</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.63763381154692</v>
+        <v>-1.624590915252554</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.4397946333430269</v>
+        <v>0.452860887643503</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.594232856183147</v>
+        <v>1.607413865478385</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.08838865162077525</v>
+        <v>-0.07518991266601205</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.385810487675556</v>
+        <v>3.399215615328387</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.181057163357856</v>
+        <v>3.194514457068074</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.674899780162932</v>
+        <v>2.688352068883042</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.423285420413301</v>
+        <v>1.412855784715148</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>183</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.151370422959431</v>
+        <v>2.163892712635054</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.738891714594871</v>
+        <v>-2.72598190501882</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.040864246328198</v>
+        <v>-2.027857114910596</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-4.096403463447544</v>
+        <v>-4.08342432104908</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.541928503656322</v>
+        <v>-3.528817699281383</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.15159039107715</v>
+        <v>-2.138547494782784</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.05053175862270365</v>
+        <v>-0.03746550432222762</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.307421454617646</v>
+        <v>3.320602463912884</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.43221391816212</v>
+        <v>5.445412657116883</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.942744470839173</v>
+        <v>2.956149598492004</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.191543059089902</v>
+        <v>2.20500035280012</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5063142207232048</v>
+        <v>-0.4928619320030947</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.9265688316681064</v>
+        <v>-0.9130127853165035</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.223295586823568</v>
+        <v>-1.23372522252172</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>181</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.112222850596716</v>
+        <v>-1.099700560921093</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5138517121798145</v>
+        <v>-0.5009419026037634</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1962519569142671</v>
+        <v>0.2092590883318692</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.641422216593583</v>
+        <v>3.654401358992047</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>6.97040431643854</v>
+        <v>6.983515120813479</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.84795675139177</v>
+        <v>2.860999647686135</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5516940929523386</v>
+        <v>-0.5386278386518626</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.191067259647383</v>
+        <v>1.204248268942621</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.632363565761437</v>
+        <v>-1.619164826806674</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.482488750789422</v>
+        <v>-2.469083623136591</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.239728262952248</v>
+        <v>-3.22627096924203</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.757831293452121</v>
+        <v>-3.744379004732011</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.835544467932927</v>
+        <v>-5.821988421581324</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.375878384275431</v>
+        <v>-3.386308019973583</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>166</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.723429149669542</v>
+        <v>1.735951439345165</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.316674813813719</v>
+        <v>1.329584623389771</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.933854299988219</v>
+        <v>3.946861431405821</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.859288155487285</v>
+        <v>2.872267297885749</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.320866940415115</v>
+        <v>2.333977744790054</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.41348960102227</v>
+        <v>1.426532497316636</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1239366066416281</v>
+        <v>0.1370028609421041</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.150475707802521</v>
+        <v>-2.137294698507283</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.1981629602320396</v>
+        <v>0.2113616991868028</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.5528570523126177</v>
+        <v>0.5662621799654488</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.552923005103395</v>
+        <v>1.566380298813613</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.9848965238946192</v>
+        <v>0.9983488126147293</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.03776772560457431</v>
+        <v>-0.02421167925297141</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.814363245226005</v>
+        <v>0.8039336095278529</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>151</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>6.446959030783404</v>
+        <v>6.459481320459027</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.822140384706486</v>
+        <v>6.835050194282537</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.129258433076856</v>
+        <v>1.142265564494458</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.06499174557399812</v>
+        <v>-0.05201260317553391</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.590167927533507</v>
+        <v>-2.577057123158568</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.680783943956989</v>
+        <v>1.693826840251354</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.920553537942915</v>
+        <v>2.933619792243391</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4666151722740679</v>
+        <v>0.4797961815693057</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.716873564237389</v>
+        <v>3.730072303192152</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.515755001726099</v>
+        <v>5.52916012937893</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.661995054891882</v>
+        <v>2.6754523486021</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.020881523495667</v>
+        <v>4.034333812215777</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.262878568179985</v>
+        <v>4.276434614531588</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.161606522972676</v>
+        <v>7.151176887274524</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>141</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.848048249287949</v>
+        <v>-2.835525959612326</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.622742429628055</v>
+        <v>-1.609832620052003</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.436050852536738</v>
+        <v>-3.423043721119136</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.9495214290069711</v>
+        <v>0.9625005714054353</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.425779218689428</v>
+        <v>-2.412668414314489</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.7098975646615955</v>
+        <v>-0.6968546683672301</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.588347441470376</v>
+        <v>5.601413695770852</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.411944184532814</v>
+        <v>4.425125193828052</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.64172444019453</v>
+        <v>3.654923179149293</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.174577978570682</v>
+        <v>9.187983106223513</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.132945221629079</v>
+        <v>6.146402515339297</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.876548237130621</v>
+        <v>6.890000525850731</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9.293173058809749</v>
+        <v>9.306729105161352</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.833674532930175</v>
+        <v>8.823244897232023</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>150</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.173228346456654</v>
+        <v>4.185750636132276</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.561654733492404</v>
+        <v>4.574564543068455</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10.16678602689578</v>
+        <v>10.17979315831338</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.425284611097879</v>
+        <v>4.438395415472819</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.389393215480176</v>
+        <v>1.402436111774541</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.637992831541226</v>
+        <v>2.651059085841702</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.170809432759683</v>
+        <v>2.18399044205492</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.109809546577424</v>
+        <v>4.123008285532187</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.926351028216281</v>
+        <v>1.939756155869112</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.388264370565324</v>
+        <v>2.401721664275541</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.244019138756059</v>
+        <v>-2.230566850035949</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.002392916965817449</v>
+        <v>0.01594896331742035</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.9187809159086555</v>
+        <v>0.9083512802105034</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>113</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.166004691891388</v>
+        <v>-1.153482402215765</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.417111960631125</v>
+        <v>3.430021770207176</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5175797548150172</v>
+        <v>-0.504572623397415</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4976291300048175</v>
+        <v>0.5106082724032817</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.8441636671450397</v>
+        <v>0.8572744715199789</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.796472861497868</v>
+        <v>3.809515757792234</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.596694896437981</v>
+        <v>4.609761150738457</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.474644241019313</v>
+        <v>1.48782525031455</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.5286886026246194</v>
+        <v>0.5418873415793826</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.5635191698090338</v>
+        <v>0.5769242974618649</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.243721597703889</v>
+        <v>1.257178891414107</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3931490028368856</v>
+        <v>0.4066012915569956</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.9120613603204077</v>
+        <v>-0.8985053139688048</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2226157241683211</v>
+        <v>0.212186088470169</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>111</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7.866922040150392</v>
+        <v>7.879444329826015</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>10.75985293169064</v>
+        <v>10.77276274126669</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.959578819688637</v>
+        <v>4.97258595110624</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.288030150494336</v>
+        <v>3.3010092928928</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.04690623271951466</v>
+        <v>0.06001703709445394</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.947951774038728</v>
+        <v>3.960994670333093</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.76411895766735</v>
+        <v>4.777185211967826</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.900539162489451</v>
+        <v>7.913720171784689</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.037737474505342</v>
+        <v>6.050936213460105</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.38581048767557</v>
+        <v>3.399215615328401</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.28015626245714</v>
+        <v>2.293613556167358</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.215440320703578</v>
+        <v>3.228892609423688</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.497888412461329</v>
+        <v>5.511444458812932</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.846708843836652</v>
+        <v>4.8362792081385</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>103</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.81724129144051</v>
+        <v>3.829763581116133</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>9.972657969738414</v>
+        <v>9.985567779314465</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.606915476734038</v>
+        <v>8.61992260815164</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.824547250118229</v>
+        <v>5.837526392516693</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.256999821453768</v>
+        <v>6.270110625828707</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.700072827130654</v>
+        <v>1.71311572342502</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.6444653234505822</v>
+        <v>0.6575315777510582</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.148155711076875</v>
+        <v>1.161336720372113</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.999777184117903</v>
+        <v>4.012975923072666</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.091399571905512</v>
+        <v>5.104804699558343</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.886646247587898</v>
+        <v>4.900103541298115</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.950155618525507</v>
+        <v>3.963607907245617</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.588153434765069</v>
+        <v>1.601709481116671</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.8670009806336836</v>
+        <v>0.8565713449355314</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>75</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>7.519083969465647</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9.894988066825725</v>
+        <v>9.907897876401776</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.83345269356251</v>
+        <v>10.84645982498011</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.96370582617001</v>
+        <v>10.97668496856847</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.75861794443118</v>
+        <v>7.771728748806119</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.389393215480212</v>
+        <v>5.402436111774577</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.304659498207933</v>
+        <v>5.317725752508409</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.504142766093061</v>
+        <v>7.517323775388299</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.443142879910759</v>
+        <v>7.456341618865522</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.593017694882867</v>
+        <v>6.606422822535698</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>15.72159770389858</v>
+        <v>15.7350549976088</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>21.08931419457738</v>
+        <v>21.10276648329749</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>19.33572625029911</v>
+        <v>19.34928229665071</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.58544758257536</v>
+        <v>15.5750179468772</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>62</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.572407421664458</v>
+        <v>5.585317231240509</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>11.62915161829369</v>
+        <v>11.64215874971129</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>14.98521120251414</v>
+        <v>14.99819034491261</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>11.22098353582906</v>
+        <v>11.234094340204</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.453909344512432</v>
+        <v>3.466952240806798</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.756272401433705</v>
+        <v>1.769338655734181</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.127798680071507</v>
+        <v>6.140979689366745</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.292605245502109</v>
+        <v>9.305803984456873</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>16.50699618950648</v>
+        <v>16.52040131715931</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.076436413576</v>
+        <v>13.08989370728622</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>17.9495292483407</v>
+        <v>17.96298153706081</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>14.30346818578298</v>
+        <v>14.31702423213459</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>19.39189919547867</v>
+        <v>19.38146955978052</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>73</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.78053428252975</v>
+        <v>7.793056572205373</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.429234642168232</v>
+        <v>3.442144451744284</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.143954976667537</v>
+        <v>7.156962108085139</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.01393413667225</v>
+        <v>10.02691327907072</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9.475512921600085</v>
+        <v>9.488623725975025</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.663365818219859</v>
+        <v>5.676408714514224</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.838906073550355</v>
+        <v>2.851972327850831</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.371722674768897</v>
+        <v>2.384903684064135</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.680585802285187</v>
+        <v>3.69378454123995</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.679775685750386</v>
+        <v>9.693180813403217</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>9.475022361432821</v>
+        <v>9.488479655143038</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9.509405518778294</v>
+        <v>9.522857807498404</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>11.82887693523062</v>
+        <v>11.84243298158222</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.338872240109623</v>
+        <v>9.328442604411471</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>57</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>12.41884238154441</v>
+        <v>12.43136467122003</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.544110873843344</v>
+        <v>5.557020683419395</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.903628132159007</v>
+        <v>6.916635263576609</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.033881264766492</v>
+        <v>7.046860407164957</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.741074084782056</v>
+        <v>4.754184889156996</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>8.547287952322272</v>
+        <v>8.560330848616637</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>15.01291469591761</v>
+        <v>15.02609570521285</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.95191480973531</v>
+        <v>14.96511354869007</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15.8561755896197</v>
+        <v>15.86958071727253</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.633878405652965</v>
+        <v>8.647335699363182</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>15.26555081170262</v>
+        <v>15.27910685805422</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.51527214397889</v>
+        <v>15.50484250828074</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-18 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-18 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2217,46 +2217,46 @@
         <v>4078</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.03562467384167434</v>
+        <v>-0.03592825547323031</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.07796262651265806</v>
+        <v>0.07762152521571153</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.0389008625536178</v>
+        <v>0.0385668047583323</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.03565883644901646</v>
+        <v>0.03532618869733994</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.02463181632019484</v>
+        <v>0.02429849917322713</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.0906664769884884</v>
+        <v>0.09031860871455422</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1417890598047578</v>
+        <v>0.1414280052018029</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.05550647669243602</v>
+        <v>0.05516359904736845</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.204067489891969</v>
+        <v>0.2036876910523517</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2008608321377281</v>
+        <v>0.2004765675328031</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.3040934136313638</v>
+        <v>0.3036824485891927</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3139607582775952</v>
+        <v>0.3274130469977052</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2018370889455099</v>
+        <v>0.2014519460745916</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.255383825831899</v>
+        <v>0.2449541901337469</v>
       </c>
     </row>
     <row r="7">
@@ -2269,46 +2269,46 @@
         <v>4047</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.008410336432859822</v>
+        <v>0.007994762959981472</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1356192305338553</v>
+        <v>0.135159399694885</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.0007358830405195249</v>
+        <v>0.0003059788262618213</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.003569293053800493</v>
+        <v>-0.003997316676070284</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.05978817449307883</v>
+        <v>-0.06020678811216129</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.004398151314326526</v>
+        <v>0.003965842837949651</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1553136576746823</v>
+        <v>0.154843225361283</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1214267167103387</v>
+        <v>0.1209607374552704</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1975678408064425</v>
+        <v>0.1970823596062559</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2010545855284178</v>
+        <v>0.2005612929398737</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2820128262114068</v>
+        <v>0.2814976853558306</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2175573376462907</v>
+        <v>0.2310096263664008</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1679476488659475</v>
+        <v>0.1815036952175504</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2694110122764073</v>
+        <v>0.2589813765782552</v>
       </c>
     </row>
     <row r="8">
@@ -2321,46 +2321,46 @@
         <v>4004</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1105985599295707</v>
+        <v>0.11001570837945</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2569023240540815</v>
+        <v>0.2562656810367514</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1498326486859227</v>
+        <v>0.149218216472299</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1440882035598676</v>
+        <v>0.1434762924278559</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.04331071902168304</v>
+        <v>0.0427179424885793</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0800119779552233</v>
+        <v>0.07941291396959826</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2834466207434545</v>
+        <v>0.2827956127878011</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2543507873944293</v>
+        <v>0.2537017805459385</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.4069381358408393</v>
+        <v>0.4062500894929073</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4698075716726962</v>
+        <v>0.4690944829601307</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.5148044971053807</v>
+        <v>0.5282617908155984</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4742625795257283</v>
+        <v>0.4877148682458383</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.4286333432062079</v>
+        <v>0.4421893895578108</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.5035295006573151</v>
+        <v>0.4930998649591629</v>
       </c>
     </row>
     <row r="9">
@@ -2373,46 +2373,46 @@
         <v>3945</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.06551722764548629</v>
+        <v>-0.06625104949768712</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3346541432234389</v>
+        <v>0.3337957013891781</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.02947158694983187</v>
+        <v>0.02868429584612642</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.07228593247221227</v>
+        <v>0.07148928705700541</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.02197277286840915</v>
+        <v>-0.02275366071046392</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.036139227128686</v>
+        <v>0.03534750417959032</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3451863472453738</v>
+        <v>0.344314762384279</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2719833201003254</v>
+        <v>0.2711231674855554</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.3517423054894024</v>
+        <v>0.3508606628651805</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.5296463387358017</v>
+        <v>0.5287069921589023</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.5783784390063076</v>
+        <v>0.5918357327165253</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.5620645114341229</v>
+        <v>0.575516800154233</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4966894949125518</v>
+        <v>0.5102455412641547</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.5182739450595548</v>
+        <v>0.5078443093614027</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3841</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2612394344677824</v>
+        <v>0.2600556504217408</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.4309901463682664</v>
+        <v>0.4297273982313428</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1543055276758736</v>
+        <v>0.1531056962217789</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2727652106520253</v>
+        <v>0.2715367626402383</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.03471922781653802</v>
+        <v>0.03354062570251415</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.176073756583186</v>
+        <v>0.1891166528775514</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.5075731298416031</v>
+        <v>0.5206393841420791</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.6012023549559231</v>
+        <v>0.5998766716768813</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.7108853751389361</v>
+        <v>0.7095292327088671</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.9687878936157972</v>
+        <v>0.9673459528497261</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.9983485500323965</v>
+        <v>1.011805843742614</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.032731707377827</v>
+        <v>1.046183996097938</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.8988608506635956</v>
+        <v>0.9124168970151985</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.7840937684644871</v>
+        <v>0.7736641327663349</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3727</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.145190128758685</v>
+        <v>0.1436153031560607</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.4501863519275915</v>
+        <v>0.4484818571143805</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.2575570444961315</v>
+        <v>0.2558917649586832</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3488711523540999</v>
+        <v>0.3471843878483796</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.06647527883718851</v>
+        <v>0.06484760492765673</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.444367739481244</v>
+        <v>0.4574106357756094</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.6814361139225653</v>
+        <v>0.6945023682230413</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.8460597904135128</v>
+        <v>0.84422106688735</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.014737549439417</v>
+        <v>1.012850917864093</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.237861626552629</v>
+        <v>1.25126675420546</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.247758154663266</v>
+        <v>1.261215448373484</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.228478848901645</v>
+        <v>1.241931137621755</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.210692711259661</v>
+        <v>1.224248757611264</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.8701269493583297</v>
+        <v>0.8596973136601775</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>3601</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.02395996282929502</v>
+        <v>-0.02599231347470976</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1830813224460854</v>
+        <v>0.1809278431054864</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.02538310259452459</v>
+        <v>0.02325693849662969</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.08746774415575231</v>
+        <v>0.08532831485756986</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1177127044626474</v>
+        <v>-0.1046019000877081</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2352693609953036</v>
+        <v>0.248312257289669</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4282362824344901</v>
+        <v>0.4413025367349661</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6275344165605148</v>
+        <v>0.6407154258557526</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7609249774762432</v>
+        <v>0.7741237164310064</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.9660622195519011</v>
+        <v>0.9794673472047322</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.9834694062034899</v>
+        <v>0.9969266999137076</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.073392691291218</v>
+        <v>1.086844980011328</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.9030686551866438</v>
+        <v>0.9166247015382467</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.7084689655245739</v>
+        <v>0.6980393298264218</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>3445</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2037774570522117</v>
+        <v>0.2010207627390557</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5222001352911008</v>
+        <v>0.5192667859145743</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.172202935388782</v>
+        <v>0.1693492940836876</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.0009772894564932244</v>
+        <v>-0.00377546865342282</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.3071778949495751</v>
+        <v>-0.2940670905746359</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.03876353343129324</v>
+        <v>-0.02572063713692785</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2248336636650734</v>
+        <v>0.2378999179655494</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3962569412260919</v>
+        <v>0.4094379505213297</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.68358796941245</v>
+        <v>0.6967867083672132</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.9655382560826311</v>
+        <v>0.9789433837354622</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.8478676603572097</v>
+        <v>0.8613249540674275</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.9403059700974197</v>
+        <v>0.9537582588175297</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.7522719687316197</v>
+        <v>0.7658280150832226</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6826899628366476</v>
+        <v>0.6722603271384955</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3266</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1220404194657689</v>
+        <v>0.1184723486705366</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5155511023214885</v>
+        <v>0.5117522661234446</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2598377563112138</v>
+        <v>0.256088547950327</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.284383515494369</v>
+        <v>0.2806335452443278</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1621822188674571</v>
+        <v>-0.1490714144925178</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.0178327490023733</v>
+        <v>-0.004789852708007913</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.3260924437069761</v>
+        <v>0.3391586980074521</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3794234356174471</v>
+        <v>0.3926044449126849</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.7470824594167738</v>
+        <v>0.760281198371537</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.121697017193505</v>
+        <v>1.135102144846336</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.070036160726502</v>
+        <v>1.08349345443672</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.0431823309317</v>
+        <v>1.05663461965181</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.9291126556879661</v>
+        <v>0.942668702039569</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.9032675458332093</v>
+        <v>0.8928379101350572</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>3074</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.03974966242641642</v>
+        <v>-0.04426885704506844</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6414119940039242</v>
+        <v>0.6365296606072164</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4919892789283651</v>
+        <v>0.4871186893060724</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.5750699554261445</v>
+        <v>0.5701809035278274</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.004117835994833285</v>
+        <v>0.01722864036977256</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.02374926988092341</v>
+        <v>-0.01070637358655802</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.2493569607973569</v>
+        <v>0.262423215097833</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.5303843622760951</v>
+        <v>0.5435653715713329</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9573480414809126</v>
+        <v>0.9705467804356758</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.473520839536917</v>
+        <v>1.486925967189748</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.171174802141913</v>
+        <v>1.18463209585213</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.173027055128202</v>
+        <v>1.186479343848312</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.045550583415569</v>
+        <v>1.059106629767172</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.197679202614431</v>
+        <v>1.187249566916279</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2899</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2469960127786521</v>
+        <v>0.2413444794587605</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8605053082050844</v>
+        <v>0.8544680246265699</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9675219128335257</v>
+        <v>0.9614023537157408</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7873231654824195</v>
+        <v>0.8003023078808837</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3178912570677142</v>
+        <v>0.3310020614426534</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2358920081673048</v>
+        <v>0.2489349044616702</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.6685780908260313</v>
+        <v>0.6816443451265073</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.8912877586192067</v>
+        <v>0.9044687679144445</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.38220232569666</v>
+        <v>1.395401064651423</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.842873967160621</v>
+        <v>1.856279094813452</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.500142029528114</v>
+        <v>1.513599323238331</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.431041226887338</v>
+        <v>1.444493515607448</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.459217109215984</v>
+        <v>1.472773155567587</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.674443788163536</v>
+        <v>1.664014152465384</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>2711</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6580544921748412</v>
+        <v>0.6509925914258616</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.020356798389187</v>
+        <v>1.012947636814644</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.014689629502513</v>
+        <v>1.007226786632032</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.6654149126079858</v>
+        <v>0.67839405500645</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2376539704978171</v>
+        <v>0.2507647748727564</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.3506621199434719</v>
+        <v>0.3637050162378372</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.077437071059244</v>
+        <v>1.09050332535972</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.237328552395766</v>
+        <v>1.250509561691004</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.729630031023497</v>
+        <v>1.74282876997826</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.244314879193652</v>
+        <v>2.257720006846483</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.002674797222078</v>
+        <v>2.016132090932295</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.852624166297495</v>
+        <v>1.866076455017605</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.838123889546615</v>
+        <v>1.851679935898218</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.050958464168907</v>
+        <v>2.040528828470755</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2501</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.06371595636876</v>
+        <v>1.054841060955859</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.632692984858551</v>
+        <v>1.623325534275523</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.63766434223637</v>
+        <v>1.650671473653972</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.448045423664347</v>
+        <v>1.461024566062811</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.6697201702075333</v>
+        <v>0.6828309745824725</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8871940951283079</v>
+        <v>0.9002369914226733</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.562156499407408</v>
+        <v>1.575222753707884</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.814685215779846</v>
+        <v>1.827866225075084</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.193509399969393</v>
+        <v>2.206708138924157</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.782808445249351</v>
+        <v>2.796213572902182</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.698007140124091</v>
+        <v>2.711464433834308</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.732390297469522</v>
+        <v>2.745842586189632</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.791943763293915</v>
+        <v>2.805499809645518</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.961697082775316</v>
+        <v>2.951267447077164</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2272</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.599871538944953</v>
+        <v>1.588595628066614</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.792875390769431</v>
+        <v>1.805785200345483</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.706105275722138</v>
+        <v>1.71911240713974</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.79234432382259</v>
+        <v>1.805323466221054</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9458245172011317</v>
+        <v>0.958935321576071</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.287280539423833</v>
+        <v>1.300323435718198</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.862758089757186</v>
+        <v>1.875824344057662</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.363884550130614</v>
+        <v>2.377065559425851</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.654997340004648</v>
+        <v>2.668196078959411</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.125294690187985</v>
+        <v>3.138699817840816</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.228639957419709</v>
+        <v>3.242097251129927</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.130980861244012</v>
+        <v>3.144433149964122</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.282909348890662</v>
+        <v>3.296465395242265</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.444602512152862</v>
+        <v>3.43417287645471</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2046</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.514381816642413</v>
+        <v>1.500520217633692</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.613463140139544</v>
+        <v>1.626372949715595</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.853980552800053</v>
+        <v>1.866987684217655</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.130861251389959</v>
+        <v>2.143840393788423</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.396936615007917</v>
+        <v>1.410047419382856</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.547750986741164</v>
+        <v>1.560793883035529</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.098403388725977</v>
+        <v>2.111469643026453</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.559861241166374</v>
+        <v>2.573042250461612</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.987619908258758</v>
+        <v>3.000818647213521</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.701522093709812</v>
+        <v>3.714927221362643</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.399017058737293</v>
+        <v>3.412474352447511</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.384524360755258</v>
+        <v>3.397976649475368</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.453028303085034</v>
+        <v>3.466584349436637</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.507246214051449</v>
+        <v>3.496816578353297</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>1835</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.947978573523002</v>
+        <v>1.960500863198625</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.843216949659549</v>
+        <v>2.8561267592356</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.938811458321823</v>
+        <v>2.951818589739425</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.450535980575097</v>
+        <v>3.463515122973561</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.585139288663697</v>
+        <v>2.598250093038637</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.392118011120495</v>
+        <v>2.40516090741486</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.179318898752847</v>
+        <v>3.192385153053323</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.584070104875984</v>
+        <v>3.597251114171222</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.959037521145994</v>
+        <v>3.972236260100757</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.743789720314254</v>
+        <v>4.757194847967085</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.266556831963968</v>
+        <v>4.280014125674185</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.191948163696331</v>
+        <v>4.205400452416441</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.262156768010286</v>
+        <v>4.275712814361889</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.457382187480029</v>
+        <v>4.446952551781877</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1650</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.779288952517298</v>
+        <v>2.791811242192921</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.349533521371228</v>
+        <v>3.362443330947279</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.439513299623115</v>
+        <v>3.452520431040718</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.690978553442733</v>
+        <v>3.703957695841197</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.152557338370563</v>
+        <v>3.165668142745503</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.843938670025629</v>
+        <v>2.856981566319995</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.48647768002607</v>
+        <v>3.499543934326546</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.807173069123358</v>
+        <v>3.820354078418596</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.412839849607721</v>
+        <v>4.426038588562484</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.896047997913136</v>
+        <v>4.909453125565967</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.388264370565253</v>
+        <v>4.40172166427547</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.362041467304621</v>
+        <v>4.375493756024731</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.366029280602142</v>
+        <v>4.379585326953745</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4.797568794696602</v>
+        <v>4.78713915899845</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1467</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.857618257840464</v>
+        <v>2.870140547516087</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.109030329947778</v>
+        <v>4.121940139523829</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.123159578361417</v>
+        <v>4.136166709779019</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.662410665979145</v>
+        <v>4.675389808377609</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.987656799236902</v>
+        <v>4.000767603611841</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.467102826932113</v>
+        <v>3.480145723226478</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.927699716340129</v>
+        <v>3.940765970640605</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.869514272568857</v>
+        <v>3.882695281864095</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.285678667231821</v>
+        <v>4.298877406186584</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.139711628079823</v>
+        <v>5.153116755732654</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.662293000422096</v>
+        <v>4.675750294132314</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.969341461107675</v>
+        <v>4.982793749827785</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.026251131008038</v>
+        <v>5.039807177359641</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5.548637766624473</v>
+        <v>5.538208130926321</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1286</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.416359502496093</v>
+        <v>3.428881792171715</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.759684800884862</v>
+        <v>4.772594610460914</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.675858084957014</v>
+        <v>4.688865216374616</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.806111217564514</v>
+        <v>4.819090359962978</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.567845523487676</v>
+        <v>3.580956327862616</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.554245470534603</v>
+        <v>3.567288366828969</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.558158720602911</v>
+        <v>4.571224974903387</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.246496317155781</v>
+        <v>4.259677326451019</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.118622402979703</v>
+        <v>5.131821141934466</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.212509659631408</v>
+        <v>6.225914787284239</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.774474842312266</v>
+        <v>5.787932136022484</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.197660487993623</v>
+        <v>6.211112776713733</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.555010853720574</v>
+        <v>6.568566900072177</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.804732185996862</v>
+        <v>6.79430255029871</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1120</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.667275965504309</v>
+        <v>3.679798255179932</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.269988066825768</v>
+        <v>5.282897876401819</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.785833645943462</v>
+        <v>4.798840777361065</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.094658207122393</v>
+        <v>5.107637349520857</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.7526655634788</v>
+        <v>3.765776367853739</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.87153607262303</v>
+        <v>3.884578968917396</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.215373783922175</v>
+        <v>5.228440038222651</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.194618956569244</v>
+        <v>5.207799965864481</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.847904784672664</v>
+        <v>5.861103523627428</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.05135102821616</v>
+        <v>7.064756155868992</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.400169132470012</v>
+        <v>6.41362642618023</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.97026657552972</v>
+        <v>6.98371886424983</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.532154821727694</v>
+        <v>7.545710868079297</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.692590439718259</v>
+        <v>7.682160804020107</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>969</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.234115859356585</v>
+        <v>3.246638149032208</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.028115001810292</v>
+        <v>5.041024811386343</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.355640516059928</v>
+        <v>5.36864764747753</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.898690346293854</v>
+        <v>5.911669488692318</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.741074084782049</v>
+        <v>4.754184889156988</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.212922627244879</v>
+        <v>4.225965523539244</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.572977351665067</v>
+        <v>5.586043605965543</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.931387348136397</v>
+        <v>5.944568357431635</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.179984985173917</v>
+        <v>6.19318372412868</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>7.290644113871473</v>
+        <v>7.304049241524304</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.982691615147296</v>
+        <v>6.996148908857514</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.429871470119139</v>
+        <v>7.443323758839249</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>8.041608603240284</v>
+        <v>8.055164649591887</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.775334063483555</v>
+        <v>7.764904427785403</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>828</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.269846703944609</v>
+        <v>4.282368993620231</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6.160688549917559</v>
+        <v>6.17359835949361</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.852776365060087</v>
+        <v>6.86578349647769</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.741483603947792</v>
+        <v>6.754462746346256</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.96151649515582</v>
+        <v>5.974627299530759</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.05122896427244</v>
+        <v>5.064271860566805</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.570359981299681</v>
+        <v>5.583426235600157</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.190133104257299</v>
+        <v>6.203314113552537</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.612225005514617</v>
+        <v>6.62542374446938</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.96982928908573</v>
+        <v>6.983234416738561</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.127394805347862</v>
+        <v>7.14085209905808</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.52409680327299</v>
+        <v>7.5375490919931</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.828479873487517</v>
+        <v>7.84203591983912</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.595109418324185</v>
+        <v>7.584679782626033</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>678</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.291222446751675</v>
+        <v>4.303744736427298</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>6.514457093374446</v>
+        <v>6.527366902950497</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.119588386777856</v>
+        <v>6.132595518195458</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6.987304646229006</v>
+        <v>7.00028378862747</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.30139080578811</v>
+        <v>6.314501610163049</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.861369616660106</v>
+        <v>5.874412512954471</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.219113775494023</v>
+        <v>6.232180029794499</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>7.07936400503111</v>
+        <v>7.092545014326348</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.165856744217535</v>
+        <v>7.179055483172299</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.085643063614384</v>
+        <v>8.099048191267215</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>8.175874990034274</v>
+        <v>8.189332283744491</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>9.685184401067019</v>
+        <v>9.698636689787129</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.559915040859572</v>
+        <v>9.573471087211175</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.072173246292209</v>
+        <v>9.061743610594057</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>565</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.38266787448029</v>
+        <v>5.395190164155913</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>7.133926119923117</v>
+        <v>7.146835929499169</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.447022015096429</v>
+        <v>7.460029146514032</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.285239749473845</v>
+        <v>8.29821889187231</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.392836233516718</v>
+        <v>7.405947037891657</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.274348967692561</v>
+        <v>6.287391863986926</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.54359755130524</v>
+        <v>6.556663805605716</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.200307957833466</v>
+        <v>8.213488967128704</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.493290372536123</v>
+        <v>8.506489111490886</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.590067842375447</v>
+        <v>9.603472970028278</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.562305668500358</v>
+        <v>9.575762962210575</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.54359148071305</v>
+        <v>11.55704376943316</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>11.65431032109557</v>
+        <v>11.66786636744717</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.84208475071699</v>
+        <v>10.83165511501884</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>454</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.77528414675038</v>
+        <v>4.787806436426003</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.247410974314754</v>
+        <v>6.260320783890805</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.05518543952433</v>
+        <v>8.068192570941932</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.50702447521553</v>
+        <v>9.520003617613995</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>9.188867577323975</v>
+        <v>9.201978381698915</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.843137708872241</v>
+        <v>6.856180605166607</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.978668308780577</v>
+        <v>6.991734563081053</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8.273599447444013</v>
+        <v>8.286780456739251</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.093656829984177</v>
+        <v>9.10685556893894</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>11.10696776830427</v>
+        <v>11.1203728959571</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.34274307834792</v>
+        <v>11.35620037205814</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>13.57976940749951</v>
+        <v>13.59322169621962</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>13.15951479655461</v>
+        <v>13.17307084290621</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>12.30791454292782</v>
+        <v>12.29748490722967</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>351</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.056419229647574</v>
+        <v>5.068941519323197</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.15424732608502</v>
+        <v>5.167157135661071</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.89328175339157</v>
+        <v>7.906288884809172</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.58763745010163</v>
+        <v>10.6006165925001</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.04921623502946</v>
+        <v>10.0623270394044</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>8.352356178443131</v>
+        <v>8.365399074737496</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8.837423030971429</v>
+        <v>8.850489285271905</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>10.36454162649192</v>
+        <v>10.37772263578716</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.58844202520989</v>
+        <v>10.60164076416466</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.87221997408511</v>
+        <v>12.88562510173794</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.2372672195681</v>
+        <v>13.25072451327831</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>16.40555351081666</v>
+        <v>16.41900579953677</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>16.55509946967234</v>
+        <v>16.56865551602394</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.66521966234747</v>
+        <v>15.65479002664932</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>276</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.390619650804517</v>
+        <v>4.40314194048014</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.866002559579393</v>
+        <v>3.878912369155444</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.094322258779897</v>
+        <v>7.107329390197499</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.48544495660479</v>
+        <v>10.49842409900325</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>10.67166142269204</v>
+        <v>10.68477222706698</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.157509157509146</v>
+        <v>9.170552053803512</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.797413121396296</v>
+        <v>9.810479375696772</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.14182392551334</v>
+        <v>11.15500493480858</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>14.57852494125964</v>
+        <v>14.59193006891248</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>12.5621774140435</v>
+        <v>12.57563470775372</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>15.1327924554469</v>
+        <v>15.14624474416701</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>15.79949436624114</v>
+        <v>15.81305041259274</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>15.68689685793771</v>
+        <v>15.67646722223956</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>214</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.385066352687218</v>
+        <v>6.397588642362841</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.371623580844464</v>
+        <v>3.384533390420515</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.780493192004883</v>
+        <v>5.793500323422485</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>9.181774361995551</v>
+        <v>9.194753504394015</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>10.51251202542805</v>
+        <v>10.52562282980299</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.80995396314371</v>
+        <v>10.82299685943808</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>12.12708940474995</v>
+        <v>12.14015565905042</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>12.59448544522079</v>
+        <v>12.60766645451603</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>12.06619583941231</v>
+        <v>12.07939457836707</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>14.01980897214139</v>
+        <v>14.03321409979422</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.41318648894531</v>
+        <v>12.42664378265553</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>14.31672852479542</v>
+        <v>14.33018081351553</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16.23292251198135</v>
+        <v>16.24647855833295</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>14.61348496575296</v>
+        <v>14.60305533005481</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>141</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5.662590048584349</v>
+        <v>5.675112338259972</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.341796577464073</v>
+        <v>3.354706387040125</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.07458744533556</v>
+        <v>5.087594576753162</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.750939868723208</v>
+        <v>8.763919011121672</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.04939808627515</v>
+        <v>11.06250889065009</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.47449959845889</v>
+        <v>13.48754249475326</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16.93586517196676</v>
+        <v>16.94893142626724</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>17.88712148949731</v>
+        <v>17.90030249879255</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>16.40768188700296</v>
+        <v>16.42088062595772</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>16.26677656013106</v>
+        <v>16.28018168778389</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.93436366134539</v>
+        <v>13.9478209550556</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>16.80562625131493</v>
+        <v>16.81907854003504</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>18.51303121483812</v>
+        <v>18.52658726118972</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>17.34431283080234</v>
+        <v>17.33388319510419</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.847369019206724</v>
+        <v>1.860278828782775</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.833452693562514</v>
+        <v>3.846459824980116</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>9.916086778550969</v>
+        <v>9.929065920949434</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>15.33004651585973</v>
+        <v>15.34315732023467</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>16.8179646440516</v>
+        <v>16.83100754034596</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>20.30465949820789</v>
+        <v>20.31772575250837</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>19.83747609942639</v>
+        <v>19.85065710872163</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>17.39552383229171</v>
+        <v>17.40872257124647</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>16.54539864726378</v>
+        <v>16.55880377491661</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>17.53112151342239</v>
+        <v>17.54457880713261</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>21.13693324219639</v>
+        <v>21.1503855309165</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>20.71667863125149</v>
+        <v>20.73023467760309</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>18.5854475825754</v>
+        <v>18.57501794687725</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-18 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-18 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3908,49 +3908,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.280988731370414</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.656892828730534</v>
+        <v>0.6698026383065852</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.9284520683422528</v>
+        <v>-0.9154449369246507</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3922772547414439</v>
+        <v>0.4052563971399081</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.044332230145464</v>
+        <v>1.057443034520404</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.039178213091262</v>
+        <v>-1.026135316796896</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.314388120839723</v>
+        <v>-2.301321866539247</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.7898570518073456</v>
+        <v>0.8030380611025834</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.88317278130765</v>
+        <v>-4.869767653654819</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-9.849830867529988</v>
+        <v>-9.83637357381977</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.46088660863551</v>
+        <v>-10.99247161194064</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.857044834038241</v>
+        <v>-4.843488787686638</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.853576807668503</v>
+        <v>-8.232210968785402</v>
       </c>
     </row>
     <row r="7">
@@ -3960,49 +3960,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.09276857634174718</v>
+        <v>0.1052908660173699</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.51880503662251</v>
+        <v>-1.505895227046459</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.6725331533326226</v>
+        <v>0.6855402847502248</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.664855251457361</v>
+        <v>1.677834393855825</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.712640932936914</v>
+        <v>3.725751737311853</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.285944939618105</v>
+        <v>2.29898783591247</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.109133605240388</v>
+        <v>-2.096067350939911</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.71424803850465</v>
+        <v>-1.701067029209412</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.499385855721428</v>
+        <v>-3.486187116766665</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.487442075232117</v>
+        <v>-3.474036947579286</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.07010609527773</v>
+        <v>-4.506428919001394</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.278308837420184</v>
+        <v>-2.737674225088419</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.857030293530798</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="8">
@@ -4012,49 +4012,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.249880639770829</v>
+        <v>-3.236873508353227</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.494627507163315</v>
+        <v>-2.481648364764851</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.09195127776451528</v>
+        <v>0.1050620821394546</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2356067845198382</v>
+        <v>-0.2225638882254728</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.537523900573611</v>
+        <v>-4.524342891278373</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.723523786755912</v>
+        <v>-7.710325047801149</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-9.19864897178384</v>
+        <v>-9.185243844131008</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-10.36645261056682</v>
+        <v>-10.6399450023912</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-9.408576100781303</v>
+        <v>-9.689686346891222</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-8.256630437598979</v>
+        <v>-8.549451880564476</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-10.90173190460409</v>
+        <v>-10.56510944165778</v>
       </c>
     </row>
     <row r="9">
@@ -4064,49 +4064,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.387840218602804</v>
+        <v>1.400362508278427</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.33332243545734</v>
+        <v>-4.320412625881289</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1619810963918269</v>
+        <v>-0.1489739649742248</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4883489683505431</v>
+        <v>-0.4753698259520789</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.256334839408346</v>
+        <v>1.269445643783286</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.6405347679915891</v>
+        <v>0.6535776642859545</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.467029999509009</v>
+        <v>-4.453963745208533</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.564350384591876</v>
+        <v>-3.551169375296638</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.538592279906595</v>
+        <v>-4.525393540951832</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-7.671822487765574</v>
+        <v>-7.658417360112743</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.571980277752793</v>
+        <v>-8.776360527505361</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.317751857650002</v>
+        <v>-8.524144831687252</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.127236712663851</v>
+        <v>-7.341961942980625</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-8.042459394168787</v>
+        <v>-7.813870942011647</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.954976781748435</v>
+        <v>-2.942454492072812</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.951165779328086</v>
+        <v>-3.938255969752035</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.576803716693895</v>
+        <v>-1.563796585276293</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.677319814855629</v>
+        <v>-2.664340672457165</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1688743546875884</v>
+        <v>0.1819851590625277</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.215545056124768</v>
+        <v>-1.366794657456239</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.850139263402021</v>
+        <v>-4.99091622280028</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.246115231842964</v>
+        <v>-6.232934222547726</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-7.235907687684708</v>
+        <v>-7.222708948729945</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-10.25321553525133</v>
+        <v>-10.2398104075985</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-10.62622838305794</v>
+        <v>-10.75410908907851</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-11.07267957489306</v>
+        <v>-11.19951094941476</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-9.476773749700889</v>
+        <v>-9.610219260981687</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-8.452169972283535</v>
+        <v>-8.299982053122754</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.129801956573608</v>
+        <v>-1.117279666897986</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.968648296810599</v>
+        <v>-2.955738487234548</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.999880639770822</v>
+        <v>-1.98687350835322</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.551445688981502</v>
+        <v>-2.538466546583038</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1353214495082184</v>
+        <v>-0.1222106451332792</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.129968971307981</v>
+        <v>-3.233927524589099</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-4.923651004075218</v>
+        <v>-5.023959896694365</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-6.532386914272237</v>
+        <v>-6.519205904976999</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-7.734939311870072</v>
+        <v>-7.721740572915309</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-9.620559726932584</v>
+        <v>-9.713211880660687</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-9.718769268578484</v>
+        <v>-9.811855757539945</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-9.577352472089323</v>
+        <v>-9.670933822512943</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-9.429250708226235</v>
+        <v>-9.524280921740093</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-6.76097274075024</v>
+        <v>-6.655396799666534</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2306390084367678</v>
+        <v>0.2431612981123905</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5021999823833667</v>
+        <v>-0.4892901728073156</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.01833406683585537</v>
+        <v>-0.005326935418253242</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2395747830859989</v>
+        <v>-0.2265956406875347</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.07786677072226</v>
+        <v>0.9925840505049948</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.9950865023328817</v>
+        <v>-1.076437127662089</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.045163823346883</v>
+        <v>-2.124955023505748</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.481107971370065</v>
+        <v>-3.559236884211238</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.15969399952187</v>
+        <v>-4.23687372036752</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-5.45197934478562</v>
+        <v>-5.528328950513981</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.566658523859431</v>
+        <v>-5.643275375392982</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.154892579041196</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.057130892558028</v>
+        <v>-5.135566188197771</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.999525583793115</v>
+        <v>-3.924982053122754</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.9072314236582528</v>
+        <v>-0.8947091339826301</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.967080898691478</v>
+        <v>-1.954171089115427</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.7067771914949645</v>
+        <v>-0.6937700600773624</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2510621480090904</v>
+        <v>0.2640412904075546</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.721785531908161</v>
+        <v>1.656786220070487</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5761152071814166</v>
+        <v>0.5129333493435908</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.5402158480524903</v>
+        <v>-0.6020529473533216</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.487073137744211</v>
+        <v>-1.548234858037375</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.723523786755912</v>
+        <v>-2.78314058178173</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.056959124774103</v>
+        <v>-4.115799399686559</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.492886975767156</v>
+        <v>-3.55284486330914</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-3.942763908630468</v>
+        <v>-4.002154593768466</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.032988833499772</v>
+        <v>-3.094232347700753</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.848118850991035</v>
+        <v>-2.793697136921637</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3916684087055486</v>
+        <v>-0.3791461190299259</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.450144676537057</v>
+        <v>-1.437234866961006</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.8494381618947173</v>
+        <v>-0.8364310304771152</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8298044983137558</v>
+        <v>-0.8168253559152916</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7951627949295172</v>
+        <v>0.7466550024934264</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3783067409790632</v>
+        <v>0.3304538304899296</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.7552739091172995</v>
+        <v>-0.802008172103605</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.051412789462503</v>
+        <v>-1.098288507260612</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.275804098213086</v>
+        <v>-2.321436158912263</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.623760330358451</v>
+        <v>-3.668697681728339</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.435592931552925</v>
+        <v>-3.480980637135083</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.34223342447028</v>
+        <v>-3.387757485487384</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.921256989924352</v>
+        <v>-2.967681989063578</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.946990896171812</v>
+        <v>-2.905428980497049</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.152547081249871</v>
+        <v>0.1650693709254938</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.459026531714386</v>
+        <v>-1.446116722138335</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.306449982836519</v>
+        <v>-1.293442851418916</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.449919477966247</v>
+        <v>-1.436940335567783</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1604444284494377</v>
+        <v>0.1233102573219327</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3254078407086922</v>
+        <v>0.2882808606329803</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3495033563209304</v>
+        <v>-0.3861133699779202</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.224794962844676</v>
+        <v>-1.260962287435738</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.336264391705498</v>
+        <v>-2.37149720897331</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.780070990132465</v>
+        <v>-3.81459764798069</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.926703489857154</v>
+        <v>-2.96219270881322</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.935195609344227</v>
+        <v>-2.970695408346259</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.57043750315075</v>
+        <v>-2.606600056290468</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.099635290352779</v>
+        <v>-3.067116367750167</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.528029515178531</v>
+        <v>-0.5155072255029083</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.667905014935236</v>
+        <v>-1.654995205359185</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.141390073733078</v>
+        <v>-2.128382942315476</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.655229395440273</v>
+        <v>-1.683692389922086</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.577340060818166</v>
+        <v>-0.6069756833995044</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3158865323527706</v>
+        <v>-0.3455953842884583</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.225308956050782</v>
+        <v>-1.254378266404167</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.808143474369984</v>
+        <v>-1.837040052161655</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.853855540310413</v>
+        <v>-2.881990399024509</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.899735928305581</v>
+        <v>-3.927542422330056</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.11384533407611</v>
+        <v>-3.14241535812242</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.958191743664933</v>
+        <v>-2.986895963959931</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.019265825770624</v>
+        <v>-3.048184053309704</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.599326406322298</v>
+        <v>-3.572367156133851</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.192068457196271</v>
+        <v>-1.179546167520648</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.639258508516697</v>
+        <v>-1.626348698940646</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.828647763058498</v>
+        <v>-1.815640631640896</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.113972949246943</v>
+        <v>-1.137470282573084</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3127126454179319</v>
+        <v>-0.3370215367776126</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4582389053159872</v>
+        <v>-0.4823375507769043</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.742043798495409</v>
+        <v>-1.765321605075705</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.104104656587353</v>
+        <v>-2.127364869300351</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.953922686343255</v>
+        <v>-2.976648071856125</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.90572054783339</v>
+        <v>-3.928194325561542</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.454710836046317</v>
+        <v>-3.477608457312058</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.177168690789067</v>
+        <v>-3.200263819732847</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.147032370390548</v>
+        <v>-3.170359329813792</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.619521361523979</v>
+        <v>-3.597395846226206</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.565850049713269</v>
+        <v>-1.553327760037646</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.219913189906734</v>
+        <v>-2.207003380330683</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.40407225653729</v>
+        <v>-2.422241551441189</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.062856985893106</v>
+        <v>-2.081199262968447</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.8912621514920858</v>
+        <v>-0.9105161083938071</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.161296646547427</v>
+        <v>-1.180297701175107</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.114308088826924</v>
+        <v>-2.132784145512034</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.549911287961002</v>
+        <v>-2.568310478313187</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.060062248294372</v>
+        <v>-3.078192915669014</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.938952639853596</v>
+        <v>-3.956878459515622</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.811494955547872</v>
+        <v>-3.829587215259515</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.865933648087719</v>
+        <v>-3.883996452923967</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.95343037620691</v>
+        <v>-3.971608732849589</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.274709138340818</v>
+        <v>-4.256307354327575</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.888493554297298</v>
+        <v>-1.875971264621676</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.94711719633213</v>
+        <v>-1.961644469731787</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.998564157411685</v>
+        <v>-2.013189297826905</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.051397791673331</v>
+        <v>-2.065969059867541</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.033509976848038</v>
+        <v>-1.048784071706706</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.393307206460754</v>
+        <v>-1.408317710049403</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.030432850077069</v>
+        <v>-2.045143445803873</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.68100330923253</v>
+        <v>-2.695517033758584</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.978410210422055</v>
+        <v>-2.992796008730394</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.536651085948748</v>
+        <v>-3.550999258816688</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.660739683727016</v>
+        <v>-3.675092993934541</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.545606440343285</v>
+        <v>-3.56002216468422</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.726211282787176</v>
+        <v>-3.740664793296382</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.978111739458498</v>
+        <v>-3.963362148411264</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.435610393552714</v>
+        <v>-1.423088103877092</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.376883993381199</v>
+        <v>-1.388764088807399</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.74693946330023</v>
+        <v>-1.758745568560187</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.968497563660499</v>
+        <v>-1.980177776529565</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.257554139098424</v>
+        <v>-1.26970251296413</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.358957397149425</v>
+        <v>-1.370997708291412</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.842912401839257</v>
+        <v>-1.854753041082589</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.332335221328329</v>
+        <v>-2.344062363225575</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.698747949096635</v>
+        <v>-2.710325047801149</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.382430841472228</v>
+        <v>-3.393891791275884</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.089928040078739</v>
+        <v>-3.10158334044597</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.077667531950695</v>
+        <v>-3.089329249657986</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.141815120859285</v>
+        <v>-3.153553242101651</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.245205208342298</v>
+        <v>-3.233492691420629</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.509691528079948</v>
+        <v>-1.518966479444138</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.072491607970974</v>
+        <v>-2.081836939680301</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.273853242510548</v>
+        <v>-2.283193576817055</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.635152132430989</v>
+        <v>-2.644319597641577</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.951750521721351</v>
+        <v>-1.961319074177467</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.760199583491115</v>
+        <v>-1.769800392081514</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.336849935754366</v>
+        <v>-2.346226240633506</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.695771433821143</v>
+        <v>-2.705089031930171</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.948845675167931</v>
+        <v>-2.958072795548901</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.561841329018698</v>
+        <v>-3.570973457864909</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.185618790946776</v>
+        <v>-3.194957883456034</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.128419654441416</v>
+        <v>-3.137783344881235</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.181900576872003</v>
+        <v>-3.191327931110358</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.382294352908474</v>
+        <v>-3.372531494223352</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.799819612322544</v>
+        <v>-1.807381957634192</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.043156263071133</v>
+        <v>-2.050881354672306</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.219039703634373</v>
+        <v>-2.226762485355593</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.345817983353797</v>
+        <v>-2.353475020853715</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.990224188690433</v>
+        <v>-1.998112521035154</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.75119455258973</v>
+        <v>-1.75913594062721</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.132766008347531</v>
+        <v>-2.140574485775993</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.380329941909061</v>
+        <v>-2.388119212295457</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.73843432353523</v>
+        <v>-2.746096112983977</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.050578168283444</v>
+        <v>-3.058255772560436</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.716921993674042</v>
+        <v>-2.724769982502579</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.701025508182745</v>
+        <v>-2.708879623613278</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.701709034447994</v>
+        <v>-2.709634900801518</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.028098234157675</v>
+        <v>-3.019964131975797</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2693</v>
+        <v>2694</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.532610530113892</v>
+        <v>-1.538913814058553</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.090224502490315</v>
+        <v>-2.096536713398628</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.2069812314868</v>
+        <v>-2.213306040700729</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.464337089109307</v>
+        <v>-2.470553690208639</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.095317412094857</v>
+        <v>-2.101745169062916</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.778322445386181</v>
+        <v>-1.784832578084831</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.9916367980884</v>
+        <v>-1.998083207136212</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.994683959854825</v>
+        <v>-2.001194743130227</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.184235425006463</v>
+        <v>-2.19068814524465</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.643912227252876</v>
+        <v>-2.650310560216994</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.383743542392217</v>
+        <v>-2.390269436948117</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.551996875305157</v>
+        <v>-2.558460025110065</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.581126013991906</v>
+        <v>-2.587637925983792</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.905454756823048</v>
+        <v>-2.898627190465</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2874</v>
+        <v>2875</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.506254392257077</v>
+        <v>-1.511386944661773</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.991359819522124</v>
+        <v>-1.99650115373327</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.056206462994389</v>
+        <v>-2.061371082850798</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.081139296345015</v>
+        <v>-2.086284413291715</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.526154861673575</v>
+        <v>-1.53155372923365</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.487775417413658</v>
+        <v>-1.493158754684011</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.901171810365518</v>
+        <v>-1.906424143397253</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.794468345018053</v>
+        <v>-1.799811478574455</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.149539764525976</v>
+        <v>-2.154769492245592</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.633760160109063</v>
+        <v>-2.638916994530447</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.437595900550498</v>
+        <v>-2.442846322752558</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.627885619979914</v>
+        <v>-2.633069456918044</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.786012880135672</v>
+        <v>-2.791190582347895</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.935081297034905</v>
+        <v>-2.92932987920971</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.330647622535551</v>
+        <v>-1.334878047561205</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.811433951522858</v>
+        <v>-1.815652729559531</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.730296896735744</v>
+        <v>-1.734579930371574</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.812250457982991</v>
+        <v>-1.816497594525586</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.316707298817974</v>
+        <v>-1.321167426057279</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.329766889506708</v>
+        <v>-1.334198850508187</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.79084427599625</v>
+        <v>-1.795135139880088</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.813869928150758</v>
+        <v>-1.818197502371255</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.021553343406154</v>
+        <v>-2.025820779908827</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.459982743137324</v>
+        <v>-2.464184730830524</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.219907389758994</v>
+        <v>-2.224209128541005</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.430738402398326</v>
+        <v>-2.434970399165024</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.635993578704507</v>
+        <v>-2.640198308214508</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.730341891108814</v>
+        <v>-2.725541079758734</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3191</v>
+        <v>3192</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.9640999931188432</v>
+        <v>-0.9676555001131391</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.40441873929349</v>
+        <v>-1.407957304621902</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.595445911476006</v>
+        <v>-1.598955931081917</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.72982744468284</v>
+        <v>-1.733287965014704</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.376798722235492</v>
+        <v>-1.380411207457556</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.187662114310392</v>
+        <v>-1.191313888225466</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.56838615532557</v>
+        <v>-1.571927264059312</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.706158558065006</v>
+        <v>-1.709693110165176</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.750432422550652</v>
+        <v>-1.753959705292544</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.083038643145343</v>
+        <v>-2.086526697697963</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.989109872807738</v>
+        <v>-1.992644532907633</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.12563517383272</v>
+        <v>-2.129126649660172</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.309637158222188</v>
+        <v>-2.313104173753288</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.262249064243782</v>
+        <v>-2.25831538645609</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3332</v>
+        <v>3333</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.043513058625521</v>
+        <v>-1.046367315650912</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.413624373365622</v>
+        <v>-1.41646684706604</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.673078366363711</v>
+        <v>-1.675868723664223</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.616784897947291</v>
+        <v>-1.619585846069072</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.421068776111575</v>
+        <v>-1.42396245406642</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.167493012064746</v>
+        <v>-1.170446258773204</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.266170091489627</v>
+        <v>-1.269100594797024</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.447724619567026</v>
+        <v>-1.45063070200014</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.522594808631851</v>
+        <v>-1.525483825512353</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.607222113270645</v>
+        <v>-1.610138959504091</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.645718637930507</v>
+        <v>-1.648638047954748</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.744918958791978</v>
+        <v>-1.747808229346226</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.818789201246041</v>
+        <v>-1.821683510187924</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.792703677928806</v>
+        <v>-1.789518506768118</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3482</v>
+        <v>3483</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.8196185777207035</v>
+        <v>-0.8218771289325275</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.157101229110125</v>
+        <v>-1.159341036330659</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.164638727374594</v>
+        <v>-1.166896404747035</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.305480886315671</v>
+        <v>-1.307693311801792</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.169864820774592</v>
+        <v>-1.17214295795219</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.057598188531294</v>
+        <v>-1.059895598337178</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.098321298582029</v>
+        <v>-1.10061235637415</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.29211105653691</v>
+        <v>-1.294370119710585</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.280306121140775</v>
+        <v>-1.282572754223168</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.455175076201506</v>
+        <v>-1.457433405358422</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.47208952709137</v>
+        <v>-1.474354067221952</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.766407198457479</v>
+        <v>-1.768586936119085</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.740357585474648</v>
+        <v>-1.742566153406692</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.675896472565327</v>
+        <v>-1.673331177440879</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3595</v>
+        <v>3596</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.8304671450436842</v>
+        <v>-0.832259893100165</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.013800400044211</v>
+        <v>-1.01560544954053</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.144362059626623</v>
+        <v>-1.146147142952607</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.248961765138361</v>
+        <v>-1.250713811242953</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.106716868739376</v>
+        <v>-1.108530150870259</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9053611558770385</v>
+        <v>-0.907219826072307</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.9196603241130461</v>
+        <v>-0.9215193210414512</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.205289798935183</v>
+        <v>-1.207088588113471</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.223523786755912</v>
+        <v>-1.22532088229157</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.391792900652966</v>
+        <v>-1.393577177464344</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.386795848074733</v>
+        <v>-1.388590459462606</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.698564593301448</v>
+        <v>-1.70027224192026</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.714329367053502</v>
+        <v>-1.716049924644814</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.616221402125575</v>
+        <v>-1.614081052010413</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3706</v>
+        <v>3707</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5708784922992436</v>
+        <v>-0.5723138799967202</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6623007981554068</v>
+        <v>-0.6637611717293979</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.9620813392596546</v>
+        <v>-0.963473831107386</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.113438056140716</v>
+        <v>-1.11478664832687</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.07224791469848</v>
+        <v>-1.073624677817499</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7603106078908581</v>
+        <v>-0.7617630806884534</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.7497439491392655</v>
+        <v>-0.7512026265977241</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9329980385046497</v>
+        <v>-0.9344223418574202</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.006331655254968</v>
+        <v>-1.007738840904594</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.248851128118069</v>
+        <v>-1.250219591907886</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.277054223844743</v>
+        <v>-1.278422091339984</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.551462504451777</v>
+        <v>-1.552756119380717</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.498371402789644</v>
+        <v>-1.499692892130298</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.422647398536313</v>
+        <v>-1.420935654417598</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3809</v>
+        <v>3810</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4526219936793581</v>
+        <v>-0.4537122638589608</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3756217211878408</v>
+        <v>-0.376769836837326</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.70406912144621</v>
+        <v>-0.705140977602106</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.9263177402086171</v>
+        <v>-0.9273289930371149</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.874523316263776</v>
+        <v>-0.8755611176510669</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6939182856987642</v>
+        <v>-0.6949970993307559</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.712111990261711</v>
+        <v>-0.71318857811778</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.8768096148593258</v>
+        <v>-0.8778544216766946</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.8711378402430654</v>
+        <v>-0.8721861225062639</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.077582882090688</v>
+        <v>-1.078597278845216</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.11051142516753</v>
+        <v>-1.11152250042425</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.402770122749686</v>
+        <v>-1.403704310686457</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.414929917679885</v>
+        <v>-1.415871206366873</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.360732517188325</v>
+        <v>-1.359365255222492</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3884</v>
+        <v>3885</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.2994429391476245</v>
+        <v>-0.3003105918478539</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1779072103816262</v>
+        <v>-0.1788355082530444</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4819088811058734</v>
+        <v>-0.4827667321725286</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6973111229825264</v>
+        <v>-0.6981117793989995</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.7082028450199758</v>
+        <v>-0.709010850577549</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.5766910599566231</v>
+        <v>-0.5775279262424178</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.5961372121493511</v>
+        <v>-0.59697106146902</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.7152231293653841</v>
+        <v>-0.7160352582791418</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.710795578990421</v>
+        <v>-0.711610394844854</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.9296160499731343</v>
+        <v>-0.9303904113719383</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.7857344288516046</v>
+        <v>-0.7865499406628089</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9686717378295882</v>
+        <v>-0.9694400170026896</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.014338099765247</v>
+        <v>-1.015102675042549</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.033501953984853</v>
+        <v>-1.032446660587361</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3946</v>
+        <v>3947</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3338020484241753</v>
+        <v>-0.3344513840697019</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.08783153903578267</v>
+        <v>-0.08856587707128938</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2921475086108458</v>
+        <v>-0.2928361157306796</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.4515284171734351</v>
+        <v>-0.4521752790938933</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.521196636268364</v>
+        <v>-0.5218337722589368</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.5134899408172586</v>
+        <v>-0.5141252030168673</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.5592413366011115</v>
+        <v>-0.5598665590748411</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.607868030128266</v>
+        <v>-0.6084878444784749</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.5538199143185523</v>
+        <v>-0.5544546024570138</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6559274527964973</v>
+        <v>-0.6565485771100086</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.5680958894161776</v>
+        <v>-0.568742470745633</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.6715773961014762</v>
+        <v>-0.6721976426415992</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.773723965054316</v>
+        <v>-0.7743245929136222</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.7125757321737183</v>
+        <v>-0.7117821544655456</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4019</v>
+        <v>4020</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1868907011623619</v>
+        <v>-0.1873380488829781</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.02413870072570745</v>
+        <v>-0.02464180613786482</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1574488779842227</v>
+        <v>-0.1579228757558511</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2619084701814387</v>
+        <v>-0.2623555607946386</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3400248890676707</v>
+        <v>-0.3404578980045088</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4015181329181416</v>
+        <v>-0.4019333023267535</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.4976256483395503</v>
+        <v>-0.498017977315321</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.5538282483996966</v>
+        <v>-0.5542112469664033</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4770029120044228</v>
+        <v>-0.4774057931427649</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.468379272554408</v>
+        <v>-0.4687925518844906</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3858115452311992</v>
+        <v>-0.3862475129554568</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4867448288828271</v>
+        <v>-0.487155611845921</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5448707646262605</v>
+        <v>-0.5452712969827118</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.5300040223014335</v>
+        <v>-0.529459665063051</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4076</v>
+        <v>4077</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.0111688166638757</v>
+        <v>-0.01147837772261795</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.05350078698232608</v>
+        <v>0.05316566803792</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.05897043668787205</v>
+        <v>-0.05928055336300986</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1601316677115392</v>
+        <v>-0.160416409785654</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2691258336186024</v>
+        <v>-0.2693872570675993</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2766204965668493</v>
+        <v>-0.2768784537089388</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3235550499184896</v>
+        <v>-0.3238021613016215</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3364582464824863</v>
+        <v>-0.3367051249300985</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2615046737933966</v>
+        <v>-0.2617704177178553</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2403156384505039</v>
+        <v>-0.2405917980638748</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2597702784500342</v>
+        <v>-0.2600430416068846</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3342594526353366</v>
+        <v>-0.3345138958804483</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.3238273430293148</v>
+        <v>-0.3240870020251094</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3056220935776963</v>
+        <v>-0.3052861983275577</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/rsi/rsi_18.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_18.xlsx
@@ -568,157 +568,157 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 22.53</t>
+          <t>X ≈ 22.54</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.770007468349988</v>
+        <v>-5.617220431609859</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.433855185016498</v>
+        <v>-7.196767577572039</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.03345591917985</v>
+        <v>4.874856660592016</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.168946390186967</v>
+        <v>5.005602805745156</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11.05632745542903</v>
+        <v>10.7547949022289</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.36353291525093</v>
+        <v>11.02981494973436</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.609907349165908</v>
+        <v>-1.506421366576561</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.534546695688348</v>
+        <v>-8.212866549368179</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.066003057579394</v>
+        <v>1.111809656910459</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1894158022943202</v>
+        <v>0.2890131932527282</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.199867506829655</v>
+        <v>3.207812561993109</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>12.91272412102638</v>
+        <v>12.6370579710165</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.805663920863886</v>
+        <v>2.872315727295295</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.586272375701924</v>
+        <v>-3.127983293554671</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 24.79</t>
+          <t>X ≈ 24.8</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-9.491816061681064</v>
+        <v>-9.298136135622208</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-11.14180689083636</v>
+        <v>-10.87852946457134</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-13.86584749872574</v>
+        <v>-13.5408092907475</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-13.73619105742281</v>
+        <v>-13.41462558867301</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-9.644174725910595</v>
+        <v>-9.370963225583886</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-7.021384687653352</v>
+        <v>-6.832702908368447</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-11.75960698989015</v>
+        <v>-11.43223115090012</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-12.23939127498639</v>
+        <v>-11.90030210618899</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-19.27983834890819</v>
+        <v>-18.74982245956215</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-24.80425016848148</v>
+        <v>-24.11847221694077</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-22.69625762303866</v>
+        <v>-22.05742683106049</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-23.6724273151511</v>
+        <v>-24.27647366880842</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-24.09257816846662</v>
+        <v>-24.67764799320034</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-21.54126112289126</v>
+        <v>-22.16207420264701</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 27.05</t>
+          <t>X ≈ 27.06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>11.8959879088087</v>
+        <v>10.78809949100065</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.927733137442928</v>
+        <v>-4.080123703501592</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.20864731596803</v>
+        <v>8.822165031041436</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4.956844702394193</v>
+        <v>5.628975892560547</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.420437851305472</v>
+        <v>5.14199012677642</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.025820399080992</v>
+        <v>2.088989631081745</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.830645830569821</v>
+        <v>-4.62557373186285</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.9111689224507202</v>
+        <v>-1.763703500064125</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>4.109831242821116</v>
+        <v>4.857295164609667</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.516860581262847</v>
+        <v>-4.289419299971975</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.722572121033735</v>
+        <v>-4.494561888454548</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-5.383109222917234</v>
+        <v>-6.103530879805</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.108344821993349</v>
+        <v>-4.834021191023652</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.4927786632922491</v>
+        <v>-1.252983293556085</v>
       </c>
     </row>
     <row r="9">
@@ -728,153 +728,153 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-12.11763599556065</v>
+        <v>-10.96379147454147</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-3.209220140637477</v>
+        <v>-3.139095369889652</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.56653300071973</v>
+        <v>-5.414886916028223</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-7.316802575589278</v>
+        <v>-8.109486720178161</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.101853219481697</v>
+        <v>-2.952776356669276</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.643761151097735</v>
+        <v>-4.564013926870352</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.16782823926664</v>
+        <v>-5.566881684083576</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-11.8706288478886</v>
+        <v>-11.685200254295</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-12.89573526761204</v>
+        <v>-13.60950636904265</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-15.67141077720151</v>
+        <v>-15.37830769380748</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-14.91879115623735</v>
+        <v>-14.64371356028155</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-16.80748992695852</v>
+        <v>-16.47535167573771</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-14.34302539565654</v>
+        <v>-14.04540476390922</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-9.309597437738141</v>
+        <v>-9.083171972801374</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 31.58</t>
+          <t>X ≈ 31.59</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4.066837880765448</v>
+        <v>3.132019061816081</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.183411797006066</v>
+        <v>-0.1783312494046712</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.207277445729687</v>
+        <v>-2.305823744433972</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.201609721138006</v>
+        <v>-2.176632104124053</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.9899778968601467</v>
+        <v>-0.9309981479629243</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-8.582213823096779</v>
+        <v>-9.335822723178964</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-5.163460104189383</v>
+        <v>-5.926520174421178</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.388470354194745</v>
+        <v>-8.129517185596541</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-9.206961298637395</v>
+        <v>-9.037037720625563</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-8.314871824806517</v>
+        <v>-8.993688254195277</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-7.142137984847345</v>
+        <v>-7.462565270311678</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.353373867580132</v>
+        <v>-6.53757711320231</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-9.282296650717313</v>
+        <v>-9.542695366108426</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.039017140842049</v>
+        <v>-2.339939815295224</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 33.84</t>
+          <t>X ≈ 33.85</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.990893299087872</v>
+        <v>5.653851623130258</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>8.09500570192391</v>
+        <v>7.957741037336618</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.904447400592503</v>
+        <v>6.785984620227744</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.830864696101514</v>
+        <v>8.476350980448231</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>4.907606871279711</v>
+        <v>5.64966577601944</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6.433309532028495</v>
+        <v>6.350831111273699</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7.930792790354637</v>
+        <v>7.851874047432005</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.660283077639406</v>
+        <v>6.609115158577396</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.835522761995122</v>
+        <v>6.573973590410823</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>9.019121235234422</v>
+        <v>8.094040190388739</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>8.814420076973875</v>
+        <v>7.111357666813092</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.674195054726027</v>
+        <v>4.828671053284516</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>10.01594896331702</v>
+        <v>8.339759270169345</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>5.479779851639506</v>
+        <v>3.903266706443908</v>
       </c>
     </row>
     <row r="12">
@@ -887,98 +887,98 @@
         <v>156</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-5.039197746528679</v>
+        <v>-4.754509063656251</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-7.290723810595267</v>
+        <v>-6.984470118949474</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.202949247384126</v>
+        <v>-2.90567950847143</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2.053036867391967</v>
+        <v>2.339968605643627</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.079421056498568</v>
+        <v>4.118119971389355</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.299872009210425</v>
+        <v>6.309786050254793</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.933110367892979</v>
+        <v>4.971964831496358</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.748093006157518</v>
+        <v>5.78844358803039</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>2.481982644506537</v>
+        <v>2.552729140659189</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.9910382071510426</v>
+        <v>1.09032641356692</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>3.991465254018905</v>
+        <v>4.088748530486413</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.025843406374378</v>
+        <v>4.147814972686227</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.246718194086604</v>
+        <v>4.394428039708387</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.267325639184641</v>
+        <v>1.439324398751594</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 38.37</t>
+          <t>X ≈ 38.38</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.707183446246319</v>
+        <v>1.608232185461809</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6563752866847139</v>
+        <v>0.5523880861063333</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.413278656354571</v>
+        <v>-0.6478846100705979</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-5.193048314408017</v>
+        <v>-5.203430805783498</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.939630655290848</v>
+        <v>-2.921531212728745</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.4076197541473832</v>
+        <v>0.1229944647047603</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.609648549167737</v>
+        <v>-1.297594839497165</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.7165788964309954</v>
+        <v>1.009979652076112</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.4617216958458457</v>
+        <v>-0.1357222031509195</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.870299710052791</v>
+        <v>-1.513329448701931</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.192319304067304</v>
+        <v>-2.828246645936581</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9233042802034745</v>
+        <v>-0.5503410157131512</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.460773569271069</v>
+        <v>-2.056689541946312</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-3.352356354798729</v>
+        <v>-2.919649960222884</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>192</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2.724026861012931</v>
+        <v>2.666021103848806</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.48598581014285</v>
+        <v>-1.533559224067439</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.442800277713978</v>
+        <v>-4.008052699831701</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.355140305607009</v>
+        <v>-4.397620357460099</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.811604584527338</v>
+        <v>-3.327442150218253</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.0899361117746551</v>
+        <v>0.0663425683170189</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.567725752508366</v>
+        <v>1.561897072293171</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.024342891278373</v>
+        <v>-2.029362054424887</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.606158381134485</v>
+        <v>-2.591361813755974</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-4.497743844131008</v>
+        <v>-4.690268076914172</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.5357783357245367</v>
+        <v>-0.9546563278069442</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.022233516702542</v>
+        <v>-1.417714636984925</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.9215510366826223</v>
+        <v>-1.29294085395275</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.82081538645609</v>
+        <v>-4.169649960222642</v>
       </c>
     </row>
     <row r="15">
@@ -1040,49 +1040,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-4.775657785757019</v>
+        <v>-4.505004382419955</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.973775009633293</v>
+        <v>-2.383572576101244</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-7.369728985686152</v>
+        <v>-7.314547604235607</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-3.241944532012219</v>
+        <v>-3.214294658509743</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-5.180652203574709</v>
+        <v>-5.40521033196471</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.311849602511174</v>
+        <v>-4.56578028343332</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-6.682274247491506</v>
+        <v>-6.894635632076948</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-5.43505717699253</v>
+        <v>-5.659685199003427</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-6.067467904944003</v>
+        <v>-6.265909126576702</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-4.631672415559585</v>
+        <v>-4.817949309428663</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.264945002391201</v>
+        <v>-4.454562479523368</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.087709707178732</v>
+        <v>-2.695032353869323</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.79357484620656</v>
+        <v>-5.363410747464947</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.710696338837039</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5.665868454279618</v>
+        <v>-5.474095310448902</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.430841702191962</v>
+        <v>-1.736367335962463</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.300604281183432</v>
+        <v>0.5357894765121713</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.558245252256299</v>
+        <v>3.339154514411113</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.488040805543697</v>
+        <v>2.315077240280615</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.406074526523341</v>
+        <v>-0.6135198440764</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.214189141108776</v>
+        <v>-4.418302700155309</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-4.085513104044331</v>
+        <v>-3.523202854725817</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.614580366949966</v>
+        <v>-3.26020575300376</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.932584269662797</v>
+        <v>-3.548418972871424</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-5.733030108774173</v>
+        <v>-5.355179041026922</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-4.634822169184815</v>
+        <v>-4.765330418564098</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.991143235264062</v>
+        <v>-4.093523852558789</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.76540758503765</v>
+        <v>-3.846566181256506</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-4.158650371881336</v>
+        <v>-4.163163415333322</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.256362465802702</v>
+        <v>-6.217367538540536</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-6.655893033567416</v>
+        <v>-6.610664243957565</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-8.642362650479036</v>
+        <v>-8.848183057554635</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-5.077007276956643</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-6.026135316796896</v>
+        <v>-6.224539911813459</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-4.68227424749152</v>
+        <v>-4.864127666437291</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.625533367468961</v>
+        <v>-5.802531955013691</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-3.781753619229825</v>
+        <v>-3.945379290168304</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.15548193936921</v>
+        <v>-4.294209286853167</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.391813084024989</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-8.611519230988264</v>
+        <v>-8.704974812266578</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-9.507860560492148</v>
+        <v>-9.577984630186862</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-8.805934434075141</v>
+        <v>-8.859618364646252</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>229</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.240750102693241</v>
+        <v>-4.503446407121977</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.1869293186107512</v>
+        <v>-0.4301425534844583</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.971641775489573</v>
+        <v>0.4822761393245187</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.954901639874031</v>
+        <v>-2.440615052067621</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.056509970262397</v>
+        <v>-2.491388704828104</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.069179608749486</v>
+        <v>-3.527408376690104</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.407165077185958</v>
+        <v>-1.848398252020232</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.620958611802394</v>
+        <v>-3.629988540672414</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.371897100202894</v>
+        <v>-2.361135532380054</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.6017285602882154</v>
+        <v>-0.5779477700618827</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.553154609378097</v>
+        <v>-2.529368896470437</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.208732788900512</v>
+        <v>-1.34069381405638</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.065564864921335</v>
+        <v>-2.176405684116247</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.839829214694802</v>
+        <v>-1.66783045512814</v>
       </c>
     </row>
     <row r="19">
@@ -1251,98 +1251,98 @@
         <v>226</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.385950892428404</v>
+        <v>2.356755098075773</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.430021770207226</v>
+        <v>3.428029498325579</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3803831288148203</v>
+        <v>0.3808716545957225</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.259303232021587</v>
+        <v>-1.2583126641183</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.125026413435769</v>
+        <v>-3.074497401838329</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.057740879375899</v>
+        <v>-1.032643523090783</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2574954864296899</v>
+        <v>-0.2084537941257878</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.6028694981020593</v>
+        <v>0.6529714266310478</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3430684106331086</v>
+        <v>-0.2683526779925884</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.07794295917536</v>
+        <v>-1.976059923882111</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.699656767520302</v>
+        <v>1.800327019096898</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.8490791676631346</v>
+        <v>0.9739058457690035</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.756361942668413</v>
+        <v>1.90505149044624</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.867053345107337</v>
+        <v>3.039052104673999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 54.21</t>
+          <t>X ≈ 54.22</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>211</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.499785396639538</v>
+        <v>-2.52898119099217</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-9.068405441133727</v>
+        <v>-9.333531827084649</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-7.567442228732261</v>
+        <v>-7.834545055781369</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-9.33295168230029</v>
+        <v>-9.60109018961645</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-8.923373936817903</v>
+        <v>-9.141545928132359</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-5.782398011448215</v>
+        <v>-6.024463935685368</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-7.28890931858168</v>
+        <v>-7.50993081031622</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-6.334177014501009</v>
+        <v>-6.558361616157505</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.447291872445589</v>
+        <v>-5.649782186360845</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-5.349343370197246</v>
+        <v>-5.533152299460966</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.132243580590149</v>
+        <v>-3.841326623875993</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.623931778945717</v>
+        <v>-3.308994711257654</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.570148982970139</v>
+        <v>-3.421459435192311</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-4.766214280610903</v>
+        <v>-4.594215521044241</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>185</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-5.453889003507264</v>
+        <v>-5.483084797859895</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.659669691165931</v>
+        <v>-1.660856477610587</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.513900535380245</v>
+        <v>-1.514053925384566</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.319027310910883</v>
+        <v>1.31853281853288</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.462505485427933</v>
+        <v>-2.413959565662161</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.624590915252554</v>
+        <v>-1.600633506302941</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.452860887643503</v>
+        <v>0.5008725666338236</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.607413865478385</v>
+        <v>1.656661427872102</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.07518991266601205</v>
+        <v>-0.001932802886315699</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.399215615328387</v>
+        <v>3.498562940622961</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.194514457068074</v>
+        <v>3.294422493086749</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.688352068883042</v>
+        <v>2.812048689911286</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.412855784715148</v>
+        <v>1.584854544281811</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>183</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.163892712635054</v>
+        <v>2.134696918282422</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.72598190501882</v>
+        <v>-2.727168691463476</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.027857114910596</v>
+        <v>-2.028010504914917</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-4.08342432104908</v>
+        <v>-4.083918813427083</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-3.528817699281383</v>
+        <v>-3.480271779515611</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.138547494782784</v>
+        <v>-2.114590085833171</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.03746550432222762</v>
+        <v>0.01054617466809304</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.320602463912884</v>
+        <v>3.369850026306601</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>5.445412657116883</v>
+        <v>5.518669766896579</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.956149598492004</v>
+        <v>3.055496923786578</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>2.20500035280012</v>
+        <v>2.304908388818795</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.4928619320030947</v>
+        <v>-0.3691653109748501</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.9130127853165035</v>
+        <v>-0.7643232375386759</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.23372522252172</v>
+        <v>-1.061726462955058</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>181</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.099700560921093</v>
+        <v>-1.128896355273724</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.5009419026037634</v>
+        <v>-0.5021286890484191</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.2092590883318692</v>
+        <v>0.2091056983275479</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3.654401358992047</v>
+        <v>3.653906866614044</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>6.983515120813479</v>
+        <v>7.032061040579251</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.860999647686135</v>
+        <v>2.884957056635749</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5386278386518626</v>
+        <v>-0.4906161596615419</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.204248268942621</v>
+        <v>1.253495831336338</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.619164826806674</v>
+        <v>-1.545907717026978</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.469083623136591</v>
+        <v>-2.369736297842017</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.22627096924203</v>
+        <v>-3.126362933223355</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.744379004732011</v>
+        <v>-3.620682383703766</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-5.821988421581324</v>
+        <v>-5.673298873803496</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.386308019973583</v>
+        <v>-3.214309260406921</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>166</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.735951439345165</v>
+        <v>1.706755644992533</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.329584623389771</v>
+        <v>1.328397836945115</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.946861431405821</v>
+        <v>3.9467080414015</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.872267297885749</v>
+        <v>2.871772805507746</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.333977744790054</v>
+        <v>2.382523664555826</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.426532497316636</v>
+        <v>1.450489906266249</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1370028609421041</v>
+        <v>0.1850145399324248</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.137294698507283</v>
+        <v>-2.088047136113566</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.2113616991868028</v>
+        <v>0.2846188089664992</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.5662621799654488</v>
+        <v>0.6656095052600222</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.566380298813613</v>
+        <v>1.666288334832288</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.9983488126147293</v>
+        <v>1.122045433642974</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.02421167925297141</v>
+        <v>0.1244778685248562</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8039336095278529</v>
+        <v>0.9759323690945152</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>151</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>6.459481320459027</v>
+        <v>6.430285526106395</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>6.835050194282537</v>
+        <v>6.833863407837882</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.142265564494458</v>
+        <v>1.142112174490137</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.05201260317553391</v>
+        <v>-0.05250709555353694</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.577057123158568</v>
+        <v>-2.528511203392796</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.693826840251354</v>
+        <v>1.717784249200967</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.933619792243391</v>
+        <v>2.981631471233712</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4797961815693057</v>
+        <v>0.5290437439630225</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.730072303192152</v>
+        <v>3.803329412971848</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.52916012937893</v>
+        <v>5.628507454673503</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.6754523486021</v>
+        <v>2.775360384620775</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.034333812215777</v>
+        <v>4.158030433244022</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.276434614531588</v>
+        <v>4.425124162309416</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.151176887274524</v>
+        <v>7.323175646841186</v>
       </c>
     </row>
     <row r="26">
@@ -1615,150 +1615,150 @@
         <v>141</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.835525959612326</v>
+        <v>-2.864721753964957</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.609832620052003</v>
+        <v>-1.611019406496659</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.423043721119136</v>
+        <v>-3.423197111123457</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.9625005714054353</v>
+        <v>0.9620060790274323</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-2.412668414314489</v>
+        <v>-2.364122494548717</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6968546683672301</v>
+        <v>-0.672897259417617</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.601413695770852</v>
+        <v>5.649425374761172</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.425125193828052</v>
+        <v>4.474372756221769</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.654923179149293</v>
+        <v>3.728180288928989</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.187983106223513</v>
+        <v>9.287330431518086</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.146402515339297</v>
+        <v>6.246310551357972</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6.890000525850731</v>
+        <v>7.013697146878975</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>9.306729105161352</v>
+        <v>9.45541865293918</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>8.823244897232023</v>
+        <v>8.995243656798685</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 70.05</t>
+          <t>X ≈ 70.06</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>150</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.185750636132276</v>
+        <v>4.156554841779645</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.574564543068455</v>
+        <v>4.573377756623799</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>10.17979315831338</v>
+        <v>10.17963976830906</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>5.642857142857139</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>4.438395415472819</v>
+        <v>4.486941335238591</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.402436111774541</v>
+        <v>1.426393520724154</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.651059085841702</v>
+        <v>2.699070764832022</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2.18399044205492</v>
+        <v>2.233238004448637</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>4.123008285532187</v>
+        <v>4.196265395311883</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>1.939756155869112</v>
+        <v>2.039103481163686</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.401721664275541</v>
+        <v>2.501629700294217</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.230566850035949</v>
+        <v>-2.106870229007704</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.01594896331742035</v>
+        <v>0.164638511095248</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.9083512802105034</v>
+        <v>1.080350039777166</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 72.31</t>
+          <t>X ≈ 72.32</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>113</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.153482402215765</v>
+        <v>-1.182678196568396</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.430021770207176</v>
+        <v>3.42883498376252</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.504572623397415</v>
+        <v>-0.5047260134017364</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.5106082724032817</v>
+        <v>0.5101137800252786</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.8572744715199789</v>
+        <v>0.9058203912857508</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>3.809515757792234</v>
+        <v>3.833473166741847</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.609761150738457</v>
+        <v>4.657772829728778</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.48782525031455</v>
+        <v>1.537072812708267</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.5418873415793826</v>
+        <v>0.6151444513590789</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.5769242974618649</v>
+        <v>0.6762716227564383</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.257178891414107</v>
+        <v>1.357086927432782</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4066012915569956</v>
+        <v>0.5302979125852403</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.8985053139688048</v>
+        <v>-0.7498157661909772</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.212186088470169</v>
+        <v>0.3841848480368313</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>111</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7.879444329826015</v>
+        <v>7.850248535473384</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>10.77276274126669</v>
+        <v>10.77157595482203</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.97258595110624</v>
+        <v>4.972432561101918</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>3.3010092928928</v>
+        <v>3.300514800514797</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.06001703709445394</v>
+        <v>0.1085629568602258</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.960994670333093</v>
+        <v>3.984952079282706</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>4.777185211967826</v>
+        <v>4.825196890958146</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>7.913720171784689</v>
+        <v>7.962967734178406</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>6.050936213460105</v>
+        <v>6.124193323239801</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>3.399215615328401</v>
+        <v>3.498562940622975</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.293613556167358</v>
+        <v>2.393521592186033</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.228892609423688</v>
+        <v>3.352589230451933</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>5.511444458812932</v>
+        <v>5.660134006590759</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>4.8362792081385</v>
+        <v>5.008277967705162</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>103</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.829763581116133</v>
+        <v>3.800567786763501</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>9.985567779314465</v>
+        <v>9.984380992869809</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.61992260815164</v>
+        <v>8.619769218147319</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.837526392516693</v>
+        <v>5.83703190013869</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.270110625828707</v>
+        <v>6.318656545594479</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.71311572342502</v>
+        <v>1.737073132374633</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.6575315777510582</v>
+        <v>0.7055432567413789</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.161336720372113</v>
+        <v>1.210584282765829</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>4.012975923072666</v>
+        <v>4.086233032852363</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>5.104804699558343</v>
+        <v>5.204152024852917</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>4.900103541298115</v>
+        <v>5.000011577316791</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.963607907245617</v>
+        <v>4.087304528273862</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.601709481116671</v>
+        <v>1.750399028894499</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.8565713449355314</v>
+        <v>1.028570104502194</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>75</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>7.519083969465647</v>
+        <v>7.489888175113016</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>9.907897876401776</v>
+        <v>9.90671108995712</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.84645982498011</v>
+        <v>10.84630643497579</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.97668496856847</v>
+        <v>10.97619047619047</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>7.771728748806119</v>
+        <v>7.820274668571891</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.402436111774577</v>
+        <v>5.42639352072419</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.317725752508409</v>
+        <v>5.365737431498729</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>7.517323775388299</v>
+        <v>7.566571337782015</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.456341618865522</v>
+        <v>7.529598728645219</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6.606422822535698</v>
+        <v>6.705770147830272</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>15.7350549976088</v>
+        <v>15.83496303362747</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>21.10276648329749</v>
+        <v>21.22646310432574</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>19.34928229665071</v>
+        <v>19.49797184442854</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.5750179468772</v>
+        <v>15.74701670644387</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>62</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.585317231240509</v>
+        <v>5.584130444795854</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>11.64215874971129</v>
+        <v>11.64200535970697</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>14.99819034491261</v>
+        <v>14.9976958525346</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>11.234094340204</v>
+        <v>11.28264025996977</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.466952240806798</v>
+        <v>3.490909649756411</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>1.769338655734181</v>
+        <v>1.817350334724502</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.140979689366745</v>
+        <v>6.190227251760462</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>9.305803984456873</v>
+        <v>9.379061094236569</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>16.52040131715931</v>
+        <v>16.61974864245389</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>13.08989370728622</v>
+        <v>13.1898017433049</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>17.96298153706081</v>
+        <v>18.08667815808905</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>14.31702423213459</v>
+        <v>14.46571377991241</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>19.38146955978052</v>
+        <v>19.55346831934718</v>
       </c>
     </row>
     <row r="33">
@@ -1979,98 +1979,98 @@
         <v>73</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>7.793056572205373</v>
+        <v>7.763860777852742</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.442144451744284</v>
+        <v>3.440957665299628</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>7.156962108085139</v>
+        <v>7.156808718080818</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.02691327907072</v>
+        <v>10.02641878669272</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9.488623725975025</v>
+        <v>9.537169645740796</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.676408714514224</v>
+        <v>5.700366123463837</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.851972327850831</v>
+        <v>2.899984006841152</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>2.384903684064135</v>
+        <v>2.434151246457851</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3.69378454123995</v>
+        <v>3.767041651019646</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>9.693180813403217</v>
+        <v>9.79252813869779</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>9.488479655143038</v>
+        <v>9.588387691161714</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>9.522857807498404</v>
+        <v>9.646554428526649</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>11.84243298158222</v>
+        <v>11.99112252936005</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>9.328442604411471</v>
+        <v>9.500441363978133</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 85.9</t>
+          <t>X ≈ 85.89</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>57</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>12.43136467122003</v>
+        <v>12.4021688768674</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>5.557020683419395</v>
+        <v>5.55583389697474</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>6.916635263576609</v>
+        <v>6.916481873572287</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.046860407164957</v>
+        <v>7.046365914786954</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>4.754184889156996</v>
+        <v>4.802730808922767</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>8.560330848616637</v>
+        <v>8.58428825756625</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>15.02609570521285</v>
+        <v>15.07534326760656</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>14.96511354869007</v>
+        <v>15.03837065846977</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15.86958071727253</v>
+        <v>15.9689280425671</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.647335699363182</v>
+        <v>8.747243735381858</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.55979643765902</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>15.27910685805422</v>
+        <v>15.42779640583205</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.50484250828074</v>
+        <v>15.6768412678474</v>
       </c>
     </row>
   </sheetData>
@@ -2214,153 +2214,153 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4078</v>
+        <v>4088</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.03592825547323031</v>
+        <v>-0.03510572881285867</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.07762152521571153</v>
+        <v>0.07744279727423731</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.0385668047583323</v>
+        <v>0.03846712457487911</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.03532618869733994</v>
+        <v>0.03524367287177199</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.02429849917322713</v>
+        <v>0.02302464823180372</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.09031860871455422</v>
+        <v>0.08947945822414738</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1414280052018029</v>
+        <v>0.1398522056134652</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.05516359904736845</v>
+        <v>0.05378840340650015</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.2036876910523517</v>
+        <v>0.2013146664251622</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2004765675328031</v>
+        <v>0.19746125242456</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.3036824485891927</v>
+        <v>0.300374913363477</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.3274130469977052</v>
+        <v>0.3234476194031259</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2014519460745916</v>
+        <v>0.2111046397330156</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2449541901337469</v>
+        <v>0.2783278610427402</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 23.66</t>
+          <t>X &gt; 23.67</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4047</v>
+        <v>4056</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.007994762959981472</v>
+        <v>0.008934623871930114</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.135159399694885</v>
+        <v>0.1348330171941328</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.0003059788262618213</v>
+        <v>0.0003102051585699428</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.003997316676070284</v>
+        <v>-0.003970205888563783</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.06020678811216129</v>
+        <v>-0.0616441506163028</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.003965842837949651</v>
+        <v>0.003165174267458326</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.154843225361283</v>
+        <v>0.1528405572678224</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1209607374552704</v>
+        <v>0.1190085608248452</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1970823596062559</v>
+        <v>0.1941312739952963</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2005612929398737</v>
+        <v>0.1967389491438567</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2814976853558306</v>
+        <v>0.2774365492717195</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.2310096263664008</v>
+        <v>0.2262988197848728</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1815036952175504</v>
+        <v>0.1901088915076699</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2589813765782552</v>
+        <v>0.3052021107831564</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 25.92</t>
+          <t>X &gt; 25.93</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4004</v>
+        <v>4012</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.11001570837945</v>
+        <v>0.1110061875353807</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2562656810367514</v>
+        <v>0.2556176505933436</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.149218216472299</v>
+        <v>0.1488169992313217</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1434762924278559</v>
+        <v>0.1431057753782667</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.0427179424885793</v>
+        <v>0.040452070544859</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.07941291396959826</v>
+        <v>0.07813481425648661</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2827956127878011</v>
+        <v>0.2798951821829334</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2537017805459385</v>
+        <v>0.2508255272626769</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.4062500894929073</v>
+        <v>0.401891484433115</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.4690944829601307</v>
+        <v>0.4634062700081927</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.5282617908155984</v>
+        <v>0.5223852005016951</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.4877148682458383</v>
+        <v>0.4950231441861916</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.4421893895578108</v>
+        <v>0.4628360358065606</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.4930998649591629</v>
+        <v>0.5516029477200775</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3945</v>
+        <v>3952</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.06625104949768712</v>
+        <v>-0.05109543144435946</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3337957013891781</v>
+        <v>0.3214436832972254</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.02868429584612642</v>
+        <v>0.01713661413299405</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.07148928705700541</v>
+        <v>0.05981827359918412</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.02275366071046392</v>
+        <v>-0.03700043030886491</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.03534750417959032</v>
+        <v>0.04760564193627204</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.344314762384279</v>
+        <v>0.3543709248050817</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2711231674855554</v>
+        <v>0.2814104821310082</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.3508606628651805</v>
+        <v>0.3342487160093839</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.5287069921589023</v>
+        <v>0.5355645529532467</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.5918357327165253</v>
+        <v>0.5985534255364513</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.575516800154233</v>
+        <v>0.5952036202589355</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.5102455412641547</v>
+        <v>0.5432539086835391</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.5078443093614027</v>
+        <v>0.579000512111925</v>
       </c>
     </row>
     <row r="10">
@@ -2422,101 +2422,101 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3841</v>
+        <v>3846</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2600556504217408</v>
+        <v>0.249670502140745</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.4297273982313428</v>
+        <v>0.4168199546539029</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1531056962217789</v>
+        <v>0.1668491711265148</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2715367626402383</v>
+        <v>0.2849733254297462</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.03354062570251415</v>
+        <v>0.04336156870159158</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1891166528775514</v>
+        <v>0.174706961305354</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.5206393841420791</v>
+        <v>0.5175671745560422</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.5998766716768813</v>
+        <v>0.611223466546285</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.7095292327088671</v>
+        <v>0.7185539783639072</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.9673459528497261</v>
+        <v>0.9741684162285011</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.011805843742614</v>
+        <v>1.018647107412875</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.046183996097938</v>
+        <v>1.065686943549537</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.9124168970151985</v>
+        <v>0.9453334248808432</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.7736641327663349</v>
+        <v>0.8453006378011594</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 32.71</t>
+          <t>X &gt; 32.72</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3727</v>
+        <v>3731</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1436153031560607</v>
+        <v>0.1608283460531865</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.4484818571143805</v>
+        <v>0.4351642024337892</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.2558917649586832</v>
+        <v>0.2430639621448591</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3471843878483796</v>
+        <v>0.3608469851453009</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.06484760492765673</v>
+        <v>0.07339409816190567</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.4574106357756094</v>
+        <v>0.4678484551985989</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.6945023682230413</v>
+        <v>0.7161922201557189</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.84422106688735</v>
+        <v>0.8806378795713243</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.012850917864093</v>
+        <v>1.01924897846677</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.25126675420546</v>
+        <v>1.281406024670929</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.261215448373484</v>
+        <v>1.280062123075787</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.241931137621755</v>
+        <v>1.300041102361234</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.224248757611264</v>
+        <v>1.268604213131653</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.8596973136601775</v>
+        <v>0.9434787809547629</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3601</v>
+        <v>3603</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.02599231347470976</v>
+        <v>-0.03431652751491754</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.1809278431054864</v>
+        <v>0.1679175094369683</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.02325693849662969</v>
+        <v>0.01062048608751809</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.08532831485756986</v>
+        <v>0.07253599114064002</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.1046019000877081</v>
+        <v>-0.124708253979577</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.248312257289669</v>
+        <v>0.2588499039974792</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4413025367349661</v>
+        <v>0.462690340085949</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.6407154258557526</v>
+        <v>0.6771282787628934</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7741237164310064</v>
+        <v>0.8219121063244401</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.9794673472047322</v>
+        <v>1.039380719866088</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.9969266999137076</v>
+        <v>1.072899805674069</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.086844980011328</v>
+        <v>1.174683169050617</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.9166247015382467</v>
+        <v>1.017394707913553</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.6980393298264218</v>
+        <v>0.83832950133705</v>
       </c>
     </row>
     <row r="13">
@@ -2578,101 +2578,101 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3445</v>
+        <v>3447</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2010207627390557</v>
+        <v>0.1793040224236009</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5192667859145743</v>
+        <v>0.4916112924448726</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.1693492940836876</v>
+        <v>0.1426027312720848</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.00377546865342282</v>
+        <v>-0.03008062848874005</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2940670905746359</v>
+        <v>-0.3167248490354453</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.02572063713692785</v>
+        <v>-0.01499577015863451</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.2378999179655494</v>
+        <v>0.258615254312808</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.4094379505213297</v>
+        <v>0.4458067852190197</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.6967867083672132</v>
+        <v>0.7435809611674244</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.9789433837354622</v>
+        <v>1.037075083597635</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.8613249540674275</v>
+        <v>0.9364123089897873</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.9537582588175297</v>
+        <v>1.040128901175031</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.7658280150832226</v>
+        <v>0.8645611715747066</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6722603271384955</v>
+        <v>0.811130428521075</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 39.5</t>
+          <t>X &gt; 39.51</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3266</v>
+        <v>3267</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1184723486705366</v>
+        <v>0.1005751980137788</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5117522661234446</v>
+        <v>0.4882627087720692</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.256088547950327</v>
+        <v>0.1861557528336562</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2806335452443278</v>
+        <v>0.254952439130804</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.1490714144925178</v>
+        <v>-0.1732093469035831</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.004789852708007913</v>
+        <v>-0.02259853791970556</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.3391586980074521</v>
+        <v>0.3443568572775462</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3926044449126849</v>
+        <v>0.414722880708986</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.760281198371537</v>
+        <v>0.7920274165017744</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.135102144846336</v>
+        <v>1.177593239647209</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.08349345443672</v>
+        <v>1.143831535156529</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.05663461965181</v>
+        <v>1.127758097697786</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.942668702039569</v>
+        <v>1.025511624110301</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.8928379101350572</v>
+        <v>1.016683067019365</v>
       </c>
     </row>
     <row r="15">
@@ -2682,49 +2682,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3074</v>
+        <v>3075</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.04426885704506844</v>
+        <v>-0.05960874147250195</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6365296606072164</v>
+        <v>0.6145032977493656</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4871186893060724</v>
+        <v>0.4480380367073948</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.5701809035278274</v>
+        <v>0.5454545454545325</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.01722864036977256</v>
+        <v>0.02373787203509181</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.01070637358655802</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.262423215097833</v>
+        <v>0.2683348340960805</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.5435653715713329</v>
+        <v>0.5673291595856327</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.9705467804356758</v>
+        <v>1.003282939171527</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.486925967189748</v>
+        <v>1.543976775510544</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.18463209585213</v>
+        <v>1.274859070014735</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.186479343848312</v>
+        <v>1.286694931863344</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.059106629767172</v>
+        <v>1.170273534935696</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.187249566916279</v>
+        <v>1.340512641403258</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2899</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2413444794587605</v>
+        <v>0.210273850044139</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.8544680246265699</v>
+        <v>0.7965182524915946</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9614023537157408</v>
+        <v>0.9193091897967349</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.8003023078808837</v>
+        <v>0.7737111373474974</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3310020614426534</v>
+        <v>0.353332519811552</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.2489349044616702</v>
+        <v>0.2473301598426048</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.6816443451265073</v>
+        <v>0.7032029962369819</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.9044687679144445</v>
+        <v>0.9453748743533765</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.395401064651423</v>
+        <v>1.444599877278343</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.856279094813452</v>
+        <v>1.93021306076384</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.513599323238331</v>
+        <v>1.622695631835605</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.444493515607448</v>
+        <v>1.528427944036146</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.472773155567587</v>
+        <v>1.566937361669922</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.664014152465384</v>
+        <v>1.801518258703304</v>
       </c>
     </row>
     <row r="17">
@@ -2786,101 +2786,101 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6509925914258616</v>
+        <v>0.6022270333082247</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.012947636814644</v>
+        <v>0.9711678118724549</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.007226786632032</v>
+        <v>0.9457539487879529</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.67839405500645</v>
+        <v>0.596816627203367</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2507647748727564</v>
+        <v>0.2180647238205111</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.3637050162378372</v>
+        <v>0.306688180024338</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.09050332535972</v>
+        <v>1.05634516630532</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.250509561691004</v>
+        <v>1.253495831336338</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.74282876997826</v>
+        <v>1.769009410044845</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.257720006846483</v>
+        <v>2.307980092581616</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.016132090932295</v>
+        <v>2.103839645045525</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.866076455017605</v>
+        <v>1.962400220513373</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.851679935898218</v>
+        <v>1.957242025040408</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.040528828470755</v>
+        <v>2.190969508803782</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 48.55</t>
+          <t>X &gt; 48.56</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2501</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.054841060955859</v>
+        <v>1.004265171918128</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.623325534275523</v>
+        <v>1.577637607529049</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.650671473653972</v>
+        <v>1.583260641578562</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.461024566062811</v>
+        <v>1.393655864901866</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.6828309745824725</v>
+        <v>0.6647901105314205</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.9002369914226733</v>
+        <v>0.8577034248775064</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.575222753707884</v>
+        <v>1.555833278144057</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.827866225075084</v>
+        <v>1.848786460252725</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2.206708138924157</v>
+        <v>2.251110975716564</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.796213572902182</v>
+        <v>2.864982075412769</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.711464433834308</v>
+        <v>2.820586036822363</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.745842586189632</v>
+        <v>2.862366686693527</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.805499809645518</v>
+        <v>2.930425881199128</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.951267447077164</v>
+        <v>3.123266206643827</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2272</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.588595628066614</v>
+        <v>1.559399833713982</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.805785200345483</v>
+        <v>1.780006294532612</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.71911240713974</v>
+        <v>1.694231350652586</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.805323466221054</v>
+        <v>1.780120671233732</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.958935321576071</v>
+        <v>0.9829084858471404</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.300323435718198</v>
+        <v>1.299688725299596</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.875824344057662</v>
+        <v>1.898953445577</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.377065559425851</v>
+        <v>2.401004539131179</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.668196078959411</v>
+        <v>2.715989695062575</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.138699817840816</v>
+        <v>3.212002733253314</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.242097251129927</v>
+        <v>3.359820050785416</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>3.144433149964122</v>
+        <v>3.28600262624974</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>3.296465395242265</v>
+        <v>3.445154943020093</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.43417287645471</v>
+        <v>3.606171636021372</v>
       </c>
     </row>
     <row r="20">
@@ -2945,98 +2945,98 @@
         <v>2046</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.500520217633692</v>
+        <v>1.471324423281061</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.626372949715595</v>
+        <v>1.597966585804741</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.866987684217655</v>
+        <v>1.839304318056719</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.143840393788423</v>
+        <v>2.115744294786793</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.410047419382856</v>
+        <v>1.431087239814353</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.560793883035529</v>
+        <v>1.557316823117887</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.111469643026453</v>
+        <v>2.131736454459123</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.573042250461612</v>
+        <v>2.59409128567323</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.000818647213521</v>
+        <v>3.045638461587735</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.714927221362643</v>
+        <v>3.785073192936892</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.412474352447511</v>
+        <v>3.532080766895675</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.397976649475368</v>
+        <v>3.541395525755433</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.466584349436637</v>
+        <v>3.615273897214465</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.496816578353297</v>
+        <v>3.668815337919959</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 55.34</t>
+          <t>X &gt; 55.35</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1835</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.960500863198625</v>
+        <v>1.931305068845994</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.8561267592356</v>
+        <v>2.854939972790945</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.951818589739425</v>
+        <v>2.951665199735103</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.463515122973561</v>
+        <v>3.463020630595558</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.598250093038637</v>
+        <v>2.646796012804408</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.40516090741486</v>
+        <v>2.429118316364473</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.192385153053323</v>
+        <v>3.240396832043643</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.597251114171222</v>
+        <v>3.646498676564939</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.972236260100757</v>
+        <v>4.045493369880454</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.757194847967085</v>
+        <v>4.856542173261658</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.280014125674185</v>
+        <v>4.379922161692861</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.205400452416441</v>
+        <v>4.329097073444686</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.275712814361889</v>
+        <v>4.424402362139716</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.446952551781877</v>
+        <v>4.618951311348539</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1650</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.791811242192921</v>
+        <v>2.76261544784029</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.362443330947279</v>
+        <v>3.361256544502623</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.452520431040718</v>
+        <v>3.452367041036396</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.703957695841197</v>
+        <v>3.703463203463194</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.165668142745503</v>
+        <v>3.214214062511275</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>2.856981566319995</v>
+        <v>2.880938975269608</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.499543934326546</v>
+        <v>3.547555613316867</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.820354078418596</v>
+        <v>3.869601640812313</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.426038588562484</v>
+        <v>4.499295698342181</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.909453125565967</v>
+        <v>5.008800450860541</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.40172166427547</v>
+        <v>4.501629700294146</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.375493756024731</v>
+        <v>4.499190377052976</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.379585326953745</v>
+        <v>4.528274874731572</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>4.78713915899845</v>
+        <v>4.959137918565112</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1467</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.870140547516087</v>
+        <v>2.840944753163456</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4.121940139523829</v>
+        <v>4.120753353079174</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.136166709779019</v>
+        <v>4.136013319774698</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.675389808377609</v>
+        <v>4.674895315999606</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.000767603611841</v>
+        <v>4.049313523377613</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.480145723226478</v>
+        <v>3.504103132176091</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.940765970640605</v>
+        <v>3.988777649630926</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.882695281864095</v>
+        <v>3.931942844257811</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.298877406186584</v>
+        <v>4.37213451596628</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.153116755732654</v>
+        <v>5.252464081027227</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.675750294132314</v>
+        <v>4.775658330150989</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.982793749827785</v>
+        <v>5.106490370856029</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.039807177359641</v>
+        <v>5.188496725137469</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5.538208130926321</v>
+        <v>5.710206890492984</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1286</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.428881792171715</v>
+        <v>3.399685997819084</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.772594610460914</v>
+        <v>4.771407824016258</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.688865216374616</v>
+        <v>4.688711826370294</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.819090359962978</v>
+        <v>4.818595867584975</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.580956327862616</v>
+        <v>3.629502247628388</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.567288366828969</v>
+        <v>3.591245775778582</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.571224974903387</v>
+        <v>4.619236653893708</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.259677326451019</v>
+        <v>4.308924888844736</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.131821141934466</v>
+        <v>5.205078251714163</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.225914787284239</v>
+        <v>6.325262112578812</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.787932136022484</v>
+        <v>5.887840172041159</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.211112776713733</v>
+        <v>6.334809397741978</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.568566900072177</v>
+        <v>6.717256447850005</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.79430255029871</v>
+        <v>6.966301309865372</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1120</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.679798255179932</v>
+        <v>3.650602460827301</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.282897876401819</v>
+        <v>5.281711089957163</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.798840777361065</v>
+        <v>4.798687387356743</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.107637349520857</v>
+        <v>5.107142857142854</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.765776367853739</v>
+        <v>3.814322287619511</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.884578968917396</v>
+        <v>3.908536377867009</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.228440038222651</v>
+        <v>5.276451717212971</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>5.207799965864481</v>
+        <v>5.257047528258198</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.861103523627428</v>
+        <v>5.934360633407124</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.064756155868992</v>
+        <v>7.164103481163565</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>6.41362642618023</v>
+        <v>6.513534462198905</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.98371886424983</v>
+        <v>7.107415485278075</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>7.545710868079297</v>
+        <v>7.694400415857125</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.682160804020107</v>
+        <v>7.854159563586769</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>969</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.246638149032208</v>
+        <v>3.217442354679577</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.041024811386343</v>
+        <v>5.039838024941687</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.36864764747753</v>
+        <v>5.368494257473209</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.911669488692318</v>
+        <v>5.911174996314315</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.754184889156988</v>
+        <v>4.80273080892276</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.225965523539244</v>
+        <v>4.249922932488857</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>5.586043605965543</v>
+        <v>5.634055284955863</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.944568357431635</v>
+        <v>5.993815919825352</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6.19318372412868</v>
+        <v>6.266440833908376</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>7.304049241524304</v>
+        <v>7.403396566818877</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.996148908857514</v>
+        <v>7.096056944876189</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.443323758839249</v>
+        <v>7.567020379867493</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>8.055164649591887</v>
+        <v>8.203854197369715</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.764904427785403</v>
+        <v>7.936903187352065</v>
       </c>
     </row>
     <row r="27">
@@ -3309,98 +3309,98 @@
         <v>828</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.282368993620231</v>
+        <v>4.2531731992676</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6.17359835949361</v>
+        <v>6.172411573048954</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.86578349647769</v>
+        <v>6.865630106473368</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.754462746346256</v>
+        <v>6.753968253968253</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.974627299530759</v>
+        <v>6.023173219296531</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.064271860566805</v>
+        <v>5.088229269516418</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>5.583426235600157</v>
+        <v>5.631437914590478</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>6.203314113552537</v>
+        <v>6.252561675946254</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>6.62542374446938</v>
+        <v>6.698680854249076</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>6.983234416738561</v>
+        <v>7.082581742033135</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>7.14085209905808</v>
+        <v>7.240760135076755</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>7.5375490919931</v>
+        <v>7.661245713021344</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>7.84203591983912</v>
+        <v>7.990725467616947</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>7.584679782626033</v>
+        <v>7.756678542192695</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 71.18</t>
+          <t>X &gt; 71.19</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>678</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.303744736427298</v>
+        <v>4.274548942074667</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>6.527366902950497</v>
+        <v>6.526180116505842</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.132595518195458</v>
+        <v>6.132442128191137</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.00028378862747</v>
+        <v>6.999789296249467</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.314501610163049</v>
+        <v>6.363047529928821</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.874412512954471</v>
+        <v>5.898369921904084</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>6.232180029794499</v>
+        <v>6.28019170878482</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>7.092545014326348</v>
+        <v>7.141792576720064</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.179055483172299</v>
+        <v>7.252312592951995</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.099048191267215</v>
+        <v>8.198395516561789</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>8.189332283744491</v>
+        <v>8.289240319763167</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>9.698636689787129</v>
+        <v>9.822333310815374</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.573471087211175</v>
+        <v>9.722160634989002</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.061743610594057</v>
+        <v>9.233742370160719</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>565</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.395190164155913</v>
+        <v>5.365994369803282</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>7.146835929499169</v>
+        <v>7.145649143054513</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.460029146514032</v>
+        <v>7.45987575650971</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.29821889187231</v>
+        <v>8.297724399494307</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>7.405947037891657</v>
+        <v>7.454492957657429</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.287391863986926</v>
+        <v>6.311349272936539</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.556663805605716</v>
+        <v>6.604675484596036</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.213488967128704</v>
+        <v>8.262736529522421</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.506489111490886</v>
+        <v>8.579746221270582</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.603472970028278</v>
+        <v>9.702820295322852</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>9.575762962210575</v>
+        <v>9.675670998229251</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>11.55704376943316</v>
+        <v>11.6807403904614</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>11.66786636744717</v>
+        <v>11.816555915225</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>10.83165511501884</v>
+        <v>11.0036538745855</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>454</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.787806436426003</v>
+        <v>4.758610642073371</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.260320783890805</v>
+        <v>6.259133997446149</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>8.068192570941932</v>
+        <v>8.06803918093761</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>9.520003617613995</v>
+        <v>9.519509125235992</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>9.201978381698915</v>
+        <v>9.250524301464687</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.856180605166607</v>
+        <v>6.88013801411622</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>6.991734563081053</v>
+        <v>7.039746242071374</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8.286780456739251</v>
+        <v>8.336028019132968</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.10685556893894</v>
+        <v>9.180112678718636</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>11.1203728959571</v>
+        <v>11.21972022125168</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.35620037205814</v>
+        <v>11.45610840807682</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>13.59322169621962</v>
+        <v>13.71691831724787</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>13.17307084290621</v>
+        <v>13.32176039068404</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>12.29748490722967</v>
+        <v>12.46948366679633</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>351</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.068941519323197</v>
+        <v>5.039745724970565</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.167157135661071</v>
+        <v>5.165970349216416</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.906288884809172</v>
+        <v>7.90613549480485</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>10.6006165925001</v>
+        <v>10.60012210012209</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>10.0623270394044</v>
+        <v>10.11087295917017</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>8.365399074737496</v>
+        <v>8.389356483687109</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8.850489285271905</v>
+        <v>8.898500964262226</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>10.37772263578716</v>
+        <v>10.42697019818088</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.60164076416466</v>
+        <v>10.67489787394435</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>12.88562510173794</v>
+        <v>12.98497242703252</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>13.25072451327831</v>
+        <v>13.35063254929699</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>16.41900579953677</v>
+        <v>16.54270242056501</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>16.56865551602394</v>
+        <v>16.71734506380177</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>15.65479002664932</v>
+        <v>15.82678878621598</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>276</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.40314194048014</v>
+        <v>4.373946146127508</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.878912369155444</v>
+        <v>3.877725582710788</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.107329390197499</v>
+        <v>7.107176000193178</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.49842409900325</v>
+        <v>10.49792960662525</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>10.68477222706698</v>
+        <v>10.73331814683275</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>9.170552053803512</v>
+        <v>9.194509462753125</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.810479375696772</v>
+        <v>9.858491054687093</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.15500493480858</v>
+        <v>11.2042524972023</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>14.59193006891248</v>
+        <v>14.69127739420705</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>12.57563470775372</v>
+        <v>12.6755427437724</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>15.14624474416701</v>
+        <v>15.26994136519526</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>15.81305041259274</v>
+        <v>15.96173996037057</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>15.67646722223956</v>
+        <v>15.84846598180622</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>214</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>6.397588642362841</v>
+        <v>6.36839284801021</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>3.384533390420515</v>
+        <v>3.383346603975859</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>5.793500323422485</v>
+        <v>5.793346933418164</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>9.194753504394015</v>
+        <v>9.194259012016012</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>10.52562282980299</v>
+        <v>10.57416874956876</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.82299685943808</v>
+        <v>10.84695426838769</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>12.14015565905042</v>
+        <v>12.18816733804074</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>12.60766645451603</v>
+        <v>12.65691401690975</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>12.07939457836707</v>
+        <v>12.15265168814677</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>14.03321409979422</v>
+        <v>14.1325614250888</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.42664378265553</v>
+        <v>12.52655181867421</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>14.33018081351553</v>
+        <v>14.45387743454378</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>16.24647855833295</v>
+        <v>16.39516810611078</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>14.60305533005481</v>
+        <v>14.77505408962147</v>
       </c>
     </row>
     <row r="34">
@@ -3673,98 +3673,98 @@
         <v>141</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5.675112338259972</v>
+        <v>5.64591654390734</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>3.354706387040125</v>
+        <v>3.353519600595469</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.087594576753162</v>
+        <v>5.08744118674884</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.763919011121672</v>
+        <v>8.763424518743669</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>11.06250889065009</v>
+        <v>11.11105481041586</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.48754249475326</v>
+        <v>13.51149990370287</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16.94893142626724</v>
+        <v>16.99694310525756</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>17.90030249879255</v>
+        <v>17.94955006118627</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>16.42088062595772</v>
+        <v>16.49413773573742</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>16.28018168778389</v>
+        <v>16.37952901307847</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.9478209550556</v>
+        <v>14.04772899107428</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>16.81907854003504</v>
+        <v>16.94277516106329</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>18.52658726118972</v>
+        <v>18.67527680896755</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>17.33388319510419</v>
+        <v>17.50588195467085</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 87.03</t>
+          <t>X &gt; 87.02</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.860278828782775</v>
+        <v>1.859092042338119</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.846459824980116</v>
+        <v>3.846306434975794</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>9.929065920949434</v>
+        <v>9.928571428571431</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>15.34315732023467</v>
+        <v>15.39170324000045</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>16.83100754034596</v>
+        <v>16.85496494929558</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>20.31772575250837</v>
+        <v>20.36573743149869</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>19.85065710872163</v>
+        <v>19.89990467111534</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>17.40872257124647</v>
+        <v>17.48197968102617</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>16.55880377491661</v>
+        <v>16.65815110021119</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>17.54457880713261</v>
+        <v>17.64448684315128</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>21.1503855309165</v>
+        <v>21.27408215194475</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>20.73023467760309</v>
+        <v>20.87892422538092</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>18.57501794687725</v>
+        <v>18.74701670644391</v>
       </c>
     </row>
   </sheetData>
@@ -3908,153 +3908,153 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.280988731370414</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.6698026383065852</v>
+        <v>0.6686158518619294</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.9154449369246507</v>
+        <v>-0.915598326928972</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.4052563971399081</v>
+        <v>0.4047619047619051</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.057443034520404</v>
+        <v>1.105988954286175</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.026135316796896</v>
+        <v>-1.002177907847283</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.301321866539247</v>
+        <v>-2.253310187548927</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.8030380611025834</v>
+        <v>0.8522856234963001</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.869767653654819</v>
+        <v>-4.770420328360245</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-9.83637357381977</v>
+        <v>-9.736465537801095</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-10.99247161194064</v>
+        <v>-10.86877499091239</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.843488787686638</v>
+        <v>-5.311551965095269</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.232210968785402</v>
+        <v>-9.824411864984661</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 23.66</t>
+          <t>X &lt; 23.67</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1052908660173699</v>
+        <v>0.07609507166473861</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.505895227046459</v>
+        <v>-1.507082013491114</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.6855402847502248</v>
+        <v>0.6853868947459034</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.677834393855825</v>
+        <v>1.677339901477822</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.725751737311853</v>
+        <v>3.774297657077625</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2.29898783591247</v>
+        <v>2.322945244862083</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.096067350939911</v>
+        <v>-2.048055671949591</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.701067029209412</v>
+        <v>-1.651819466815695</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.486187116766665</v>
+        <v>-3.412930006986969</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.474036947579286</v>
+        <v>-3.374689622284713</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.506428919001394</v>
+        <v>-4.382732297973149</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.737674225088419</v>
+        <v>-3.053752293502498</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-7.977121224590576</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 25.92</t>
+          <t>X &lt; 25.93</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.236873508353227</v>
+        <v>-3.237026898357549</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.481648364764851</v>
+        <v>-2.482142857142854</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1050620821394546</v>
+        <v>0.1536080019052264</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.2225638882254728</v>
+        <v>-0.1986064792758597</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.524342891278373</v>
+        <v>-4.475095328884656</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-7.710325047801149</v>
+        <v>-7.637067938021453</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-9.185243844131008</v>
+        <v>-9.085896518836435</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-10.6399450023912</v>
+        <v>-10.54003696637253</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-9.689686346891222</v>
+        <v>-9.856870229007633</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-8.549451880564476</v>
+        <v>-9.002028155571459</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-10.56510944165778</v>
+        <v>-11.87798329355609</v>
       </c>
     </row>
     <row r="9">
@@ -4064,49 +4064,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.400362508278427</v>
+        <v>1.126251811476656</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.320412625881289</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1489739649742248</v>
+        <v>0.05842764709699821</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.4753698259520789</v>
+        <v>-0.2662337662337748</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.269445643783286</v>
+        <v>1.517244365541579</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.6535776642859545</v>
+        <v>0.4263935207241545</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-4.453963745208533</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.551169375296638</v>
+        <v>-3.736458965248289</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.525393540951832</v>
+        <v>-4.227977028930546</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-7.658417360112743</v>
+        <v>-7.779078337018255</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.776360527505361</v>
+        <v>-8.892309693645252</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-8.524144831687252</v>
+        <v>-8.83414295628036</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.341961942980625</v>
+        <v>-7.865664519207819</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.813870942011647</v>
+        <v>-8.980256020828818</v>
       </c>
     </row>
     <row r="10">
@@ -4116,101 +4116,101 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.942454492072812</v>
+        <v>-2.81686029114465</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.938255969752035</v>
+        <v>-3.786540443785171</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.563796585276293</v>
+        <v>-1.726290702038526</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.664340672457165</v>
+        <v>-2.823400525854517</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1819851590625277</v>
+        <v>0.06158346202792586</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.366794657456239</v>
+        <v>-1.199373350441491</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.99091622280028</v>
+        <v>-4.941011034758979</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.232934222547726</v>
+        <v>-6.327089193915327</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-7.222708948729945</v>
+        <v>-7.284307201825129</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-10.2398104075985</v>
+        <v>-10.2553750464438</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-10.75410908907851</v>
+        <v>-10.76626396023756</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-11.19951094941476</v>
+        <v>-11.321594155388</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-9.610219260981687</v>
+        <v>-9.876261284405821</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-8.299982053122754</v>
+        <v>-9.013719489875108</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 32.71</t>
+          <t>X &lt; 32.72</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.117279666897986</v>
+        <v>-1.262946292007157</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.955738487234548</v>
+        <v>-2.846123377163011</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-1.98687350835322</v>
+        <v>-1.879317147790651</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.538466546583038</v>
+        <v>-2.656462585034014</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1222106451332792</v>
+        <v>-0.1978659209972804</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-3.233927524589099</v>
+        <v>-3.326440946396026</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-5.023959896694365</v>
+        <v>-5.201155992537593</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-6.519205904976999</v>
+        <v>-6.800775600993504</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-7.721740572915309</v>
+        <v>-7.74477768858835</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-9.713211880660687</v>
+        <v>-9.929150487090403</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-9.811855757539945</v>
+        <v>-9.906533565011983</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-9.670933822512943</v>
+        <v>-10.0751241972616</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-9.524280921740093</v>
+        <v>-9.790010014981888</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-6.655396799666534</v>
+        <v>-7.2733914568214</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2431612981123905</v>
+        <v>0.2969057189726598</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.4892901728073156</v>
+        <v>-0.4090783837270493</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.005326935418253242</v>
+        <v>0.07437661041439014</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2265956406875347</v>
+        <v>-0.1466165413533886</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.9925840505049948</v>
+        <v>1.118520282606973</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1.076437127662089</v>
+        <v>-1.146541452913809</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.124955023505748</v>
+        <v>-2.261679088712214</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.559236884211238</v>
+        <v>-3.781993395668493</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-4.23687372036752</v>
+        <v>-4.52195370252057</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-5.528328950513981</v>
+        <v>-5.873023056622017</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.643275375392982</v>
+        <v>-6.077163504158108</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.721984464508516</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.135566188197771</v>
+        <v>-5.711166995641754</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.924982053122754</v>
+        <v>-4.759134435911108</v>
       </c>
     </row>
     <row r="13">
@@ -4272,101 +4272,101 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>716</v>
+        <v>725</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.8947091339826301</v>
+        <v>-0.7907170518470892</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.954171089115427</v>
+        <v>-1.823687809630179</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.6937700600773624</v>
+        <v>-0.5668068158265953</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.2640412904075546</v>
+        <v>0.3883867164472434</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.656786220070487</v>
+        <v>1.765178249839103</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5129333493435908</v>
+        <v>0.4608762793448307</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.6020529473533216</v>
+        <v>-0.703228085742694</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.548234858037375</v>
+        <v>-1.720784984057069</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.78314058178173</v>
+        <v>-2.999136903538698</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-4.115799399686559</v>
+        <v>-4.374689622284713</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.55284486330914</v>
+        <v>-3.88917489740701</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-4.002154593768466</v>
+        <v>-4.382732297973149</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.094232347700753</v>
+        <v>-3.536510914192149</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.793697136921637</v>
+        <v>-3.425397086659544</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 39.5</t>
+          <t>X &lt; 39.51</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.3791461190299259</v>
+        <v>-0.3123096270847796</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.437234866961006</v>
+        <v>-1.346036162790085</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.8364310304771152</v>
+        <v>-0.58163635930363</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8168253559152916</v>
+        <v>-0.7227816236626836</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.7466550024934264</v>
+        <v>0.831667538840172</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.3304538304899296</v>
+        <v>0.3932809379426914</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.802008172103605</v>
+        <v>-0.8221078723687185</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.098288507260612</v>
+        <v>-1.177443395182998</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.321436158912263</v>
+        <v>-2.429885617579458</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.668697681728339</v>
+        <v>-3.806200386239745</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.480980637135083</v>
+        <v>-3.678849121068659</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.387757485487384</v>
+        <v>-3.620682383703766</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.967681989063578</v>
+        <v>-3.242359647284168</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-2.905428980497049</v>
+        <v>-3.324806497975985</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1087</v>
+        <v>1097</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1650693709254938</v>
+        <v>0.2072794794608441</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.446116722138335</v>
+        <v>-1.375897605695009</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.293442851418916</v>
+        <v>-1.177870053389277</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.436940335567783</v>
+        <v>-1.362587503240867</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.1233102573219327</v>
+        <v>0.1036534151658941</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.2882808606329803</v>
+        <v>0.3354844298150539</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3861133699779202</v>
+        <v>-0.403143369229241</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.260962287435738</v>
+        <v>-1.323935183297763</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.37149720897331</v>
+        <v>-2.452809521278958</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.81459764798069</v>
+        <v>-3.957253531586893</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.96219270881322</v>
+        <v>-3.202411624531138</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.970695408346259</v>
+        <v>-3.235402589992134</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.606600056290468</v>
+        <v>-2.901298893948855</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.067116367750167</v>
+        <v>-3.472673357366482</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1262</v>
+        <v>1273</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.5155072255029083</v>
+        <v>-0.441415493895569</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.654995205359185</v>
+        <v>-1.515163910042837</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.128382942315476</v>
+        <v>-2.024165287724237</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.683692389922086</v>
+        <v>-1.618488710038015</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6069756833995044</v>
+        <v>-0.6568853418692555</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3455953842884583</v>
+        <v>-0.3416315576457549</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.254378266404167</v>
+        <v>-1.300929235167978</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.837040052161655</v>
+        <v>-1.923624740649366</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.881990399024509</v>
+        <v>-2.980205192923407</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-3.927542422330056</v>
+        <v>-4.077066063577405</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.14241535812242</v>
+        <v>-3.376348828116434</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.986895963959931</v>
+        <v>-3.161072899863882</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.048184053309704</v>
+        <v>-3.242012444652374</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.572367156133851</v>
+        <v>-3.857068132519167</v>
       </c>
     </row>
     <row r="17">
@@ -4480,101 +4480,101 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1450</v>
+        <v>1460</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.179546167520648</v>
+        <v>-1.08154039631556</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.626348698940646</v>
+        <v>-1.540531932507093</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.815640631640896</v>
+        <v>-1.694111367022394</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.137470282573084</v>
+        <v>-0.9829097283084991</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.3370215367776126</v>
+        <v>-0.2761327893635368</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4823375507769043</v>
+        <v>-0.3756542608458204</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.765321605075705</v>
+        <v>-1.697104098555954</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.127364869300351</v>
+        <v>-2.126752881857996</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.976648071856125</v>
+        <v>-3.016684901085753</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.928194325561542</v>
+        <v>-4.010177833004818</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.477608457312058</v>
+        <v>-3.630790391030054</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.200263819732847</v>
+        <v>-3.367144201610373</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.170359329813792</v>
+        <v>-3.351343224064607</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.597395846226206</v>
+        <v>-3.855723019583493</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 48.55</t>
+          <t>X &lt; 48.56</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1660</v>
+        <v>1671</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.553327760037646</v>
+        <v>-1.46906482905117</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.207003380330683</v>
+        <v>-2.129003195757122</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.422241551441189</v>
+        <v>-2.313113854879283</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.081199262968447</v>
+        <v>-1.97335263068279</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.9105161083938071</v>
+        <v>-0.8809775675640665</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.180297701175107</v>
+        <v>-1.112985954216185</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.132784145512034</v>
+        <v>-2.096949135665497</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.568310478313187</v>
+        <v>-2.59113475540795</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.078192915669014</v>
+        <v>-3.134677023496643</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.956878459515622</v>
+        <v>-4.047020920750313</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.829587215259515</v>
+        <v>-3.980716200364149</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.883996452923967</v>
+        <v>-4.042238272095602</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.971608732849589</v>
+        <v>-4.13817417591855</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.256307354327575</v>
+        <v>-4.487573359384932</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1889</v>
+        <v>1900</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.875971264621676</v>
+        <v>-1.83019550689535</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.961644469731787</v>
+        <v>-1.921651024119235</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.013189297826905</v>
+        <v>-1.973937893121942</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.065969059867541</v>
+        <v>-2.026079473172196</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.048784071706706</v>
+        <v>-1.072807092434402</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.408317710049403</v>
+        <v>-1.401084192962266</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.045143445803873</v>
+        <v>-2.063433607326083</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.695517033758584</v>
+        <v>-2.711643885315105</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.992796008730394</v>
+        <v>-3.036227601886992</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.550999258816688</v>
+        <v>-3.622483486781782</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-3.675092993934541</v>
+        <v>-3.799106367003446</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.56002216468422</v>
+        <v>-3.713393111700945</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.740664793296382</v>
+        <v>-3.898135467512539</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.963362148411264</v>
+        <v>-4.147720135661359</v>
       </c>
     </row>
     <row r="20">
@@ -4636,101 +4636,101 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2115</v>
+        <v>2126</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.423088103877092</v>
+        <v>-1.387567390836473</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.388764088807399</v>
+        <v>-1.355806458007272</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.758745568560187</v>
+        <v>-1.724854613713347</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.980177776529565</v>
+        <v>-1.944964871194379</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.26970251296413</v>
+        <v>-1.285004931553068</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.370997708291412</v>
+        <v>-1.362167191887202</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.854753041082589</v>
+        <v>-1.866907971878426</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-2.344062363225575</v>
+        <v>-2.354905277265694</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.710325047801149</v>
+        <v>-2.742701740838356</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.393891791275884</v>
+        <v>-3.447979656459736</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.10158334044597</v>
+        <v>-3.20451065058306</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.089329249657986</v>
+        <v>-3.215473896144452</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.153553242101651</v>
+        <v>-3.281529801081575</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.233492691420629</v>
+        <v>-3.383745287911687</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 55.34</t>
+          <t>X &lt; 55.35</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2326</v>
+        <v>2337</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.518966479444138</v>
+        <v>-1.488835229142303</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.081836939680301</v>
+        <v>-2.071151830434495</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.283193576817055</v>
+        <v>-2.272376131747656</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.644319597641577</v>
+        <v>-2.631535699068721</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.961319074177467</v>
+        <v>-1.990467019407653</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.769800392081514</v>
+        <v>-1.780429506994402</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.346226240633506</v>
+        <v>-2.373170418330659</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.705089031930171</v>
+        <v>-2.731337326323832</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.958072795548901</v>
+        <v>-3.002140525553472</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.570973457864909</v>
+        <v>-3.632831589319132</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.194957883456034</v>
+        <v>-3.259054060389616</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.137783344881235</v>
+        <v>-3.221021575737005</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.191327931110358</v>
+        <v>-3.294158181234415</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.372531494223352</v>
+        <v>-3.493034641437987</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2511</v>
+        <v>2522</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.807381957634192</v>
+        <v>-1.780328787411641</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.050881354672306</v>
+        <v>-2.041197355188849</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.226762485355593</v>
+        <v>-2.216991367366617</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.353475020853715</v>
+        <v>-2.342924847664186</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.998112521035154</v>
+        <v>-2.021421630651076</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.75913594062721</v>
+        <v>-1.767282368603922</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.140574485775993</v>
+        <v>-2.162930025994392</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.388119212295457</v>
+        <v>-2.410221911163134</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.746096112983977</v>
+        <v>-2.782497300902342</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.058255772560436</v>
+        <v>-3.110540224299619</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.724769982502579</v>
+        <v>-2.778898352511135</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.708879623613278</v>
+        <v>-2.778819515853904</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.709634900801518</v>
+        <v>-2.796122487715735</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.019964131975797</v>
+        <v>-3.120548717822544</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2694</v>
+        <v>2705</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.538913814058553</v>
+        <v>-1.516734341443268</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.096536713398628</v>
+        <v>-2.087400062048729</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.213306040700729</v>
+        <v>-2.204258120743397</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.470553690208639</v>
+        <v>-2.460273612207324</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.101745169062916</v>
+        <v>-2.119789197800017</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.784832578084831</v>
+        <v>-1.790709317462358</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.998083207136212</v>
+        <v>-2.016268468206327</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.001194743130227</v>
+        <v>-2.020051064775473</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.19068814524465</v>
+        <v>-2.221938786729936</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.650310560216994</v>
+        <v>-2.694008368227351</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.390269436948117</v>
+        <v>-2.435347158396162</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.558460025110065</v>
+        <v>-2.615920838538479</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.587637925983792</v>
+        <v>-2.658716995187127</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.898627190465</v>
+        <v>-2.981264254739095</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2875</v>
+        <v>2886</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.511386944661773</v>
+        <v>-1.492519551689327</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.99650115373327</v>
+        <v>-1.988388979055948</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2.061371082850798</v>
+        <v>-2.053474948064128</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.086284413291715</v>
+        <v>-2.078137332280981</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.53155372923365</v>
+        <v>-1.547600979096508</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.493158754684011</v>
+        <v>-1.498278213899212</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.906424143397253</v>
+        <v>-1.920816318933397</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.799811478574455</v>
+        <v>-1.815171400807202</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.154769492245592</v>
+        <v>-2.17961376991353</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.638916994530447</v>
+        <v>-2.673699287002528</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.442846322752558</v>
+        <v>-2.478640289321639</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.633069456918044</v>
+        <v>-2.678892389672448</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.791190582347895</v>
+        <v>-2.847715720517776</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.92932987920971</v>
+        <v>-2.995880036452839</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3041</v>
+        <v>3052</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.334878047561205</v>
+        <v>-1.319247224560712</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.815652729559531</v>
+        <v>-1.808693609781741</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.734579930371574</v>
+        <v>-1.728293630319669</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.816497594525586</v>
+        <v>-1.809788186992634</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.321167426057279</v>
+        <v>-1.334467790319543</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.334198850508187</v>
+        <v>-1.338312361628795</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.795135139880088</v>
+        <v>-1.806541090894257</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.818197502371255</v>
+        <v>-1.829984145104412</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.025820779908827</v>
+        <v>-2.045801991014578</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.464184730830524</v>
+        <v>-2.492310131401879</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.224209128541005</v>
+        <v>-2.253416671773508</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.434970399165024</v>
+        <v>-2.472292625864213</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.640198308214508</v>
+        <v>-2.686109387146963</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.725541079758734</v>
+        <v>-2.779850921341158</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3192</v>
+        <v>3203</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.9676555001131391</v>
+        <v>-0.9553854567277753</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.407957304621902</v>
+        <v>-1.402775690758233</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.598955931081917</v>
+        <v>-1.593436356976092</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.733287965014704</v>
+        <v>-1.727201991907883</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.380411207457556</v>
+        <v>-1.390601213536868</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.191313888225466</v>
+        <v>-1.194596824962552</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.571927264059312</v>
+        <v>-1.581303066943683</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.709693110165176</v>
+        <v>-1.718979716544368</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.753959705292544</v>
+        <v>-1.770484396874323</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.086526697697963</v>
+        <v>-2.10994547424648</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.992644532907633</v>
+        <v>-2.016565350651994</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.129126649660172</v>
+        <v>-2.159912350692508</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.313104173753288</v>
+        <v>-2.350966982038372</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.25831538645609</v>
+        <v>-2.30356087707154</v>
       </c>
     </row>
     <row r="27">
@@ -5000,101 +5000,101 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3333</v>
+        <v>3344</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.046367315650912</v>
+        <v>-1.035580993787789</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.41646684706604</v>
+        <v>-1.41152490527525</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.675868723664223</v>
+        <v>-1.670335393141443</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.619585846069072</v>
+        <v>-1.614149416475001</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.42396245406642</v>
+        <v>-1.431539627083744</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.170446258773204</v>
+        <v>-1.172651825337901</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.269100594797024</v>
+        <v>-1.277055764562185</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.45063070200014</v>
+        <v>-1.458304284108536</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.525483825512353</v>
+        <v>-1.538978956235844</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.610138959504091</v>
+        <v>-1.629952671763562</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.648638047954748</v>
+        <v>-1.668472879130221</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.747808229346226</v>
+        <v>-1.773337652797238</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.821683510187924</v>
+        <v>-1.853298708635727</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.789518506768118</v>
+        <v>-1.827145972981924</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 71.18</t>
+          <t>X &lt; 71.19</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3483</v>
+        <v>3494</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.8218771289325275</v>
+        <v>-0.8135050384598372</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.159341036330659</v>
+        <v>-1.155468031548821</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.166896404747035</v>
+        <v>-1.163203788514458</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.307693311801792</v>
+        <v>-1.303489889106338</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.17214295795219</v>
+        <v>-1.178107670375688</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.059895598337178</v>
+        <v>-1.061327781388933</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.10061235637415</v>
+        <v>-1.106699015230816</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.294370119710585</v>
+        <v>-1.300095328884652</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.282572754223168</v>
+        <v>-1.293112522188352</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.457433405358422</v>
+        <v>-1.472617502255538</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.474354067221952</v>
+        <v>-1.489600878297033</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.768586936119085</v>
+        <v>-1.787648261044254</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.742566153406692</v>
+        <v>-1.766691961007794</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.673331177440879</v>
+        <v>-1.702325022233822</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3596</v>
+        <v>3607</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.832259893100165</v>
+        <v>-0.8250289519588065</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-1.01560544954053</v>
+        <v>-1.012327318442949</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.146147142952607</v>
+        <v>-1.142637733072853</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.250713811242953</v>
+        <v>-1.246830443540425</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.108530150870259</v>
+        <v>-1.11298491844876</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.907219826072307</v>
+        <v>-0.9083229384736384</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.9215193210414512</v>
+        <v>-0.9264595801227884</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.207088588113471</v>
+        <v>-1.211360205718314</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.22532088229157</v>
+        <v>-1.233413452971618</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.393577177464344</v>
+        <v>-1.405371733458431</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.388590459462606</v>
+        <v>-1.400494030084438</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.70027224192026</v>
+        <v>-1.715071946935034</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.716049924644814</v>
+        <v>-1.734844120094735</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.614081052010413</v>
+        <v>-1.636958896550269</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3707</v>
+        <v>3718</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.5723138799967202</v>
+        <v>-0.5669330524399214</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6637611717293979</v>
+        <v>-0.6616535213028882</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.963473831107386</v>
+        <v>-0.9606123099960513</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.11478664832687</v>
+        <v>-1.11143470263643</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.073624677817499</v>
+        <v>-1.076603964824052</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7617630806884534</v>
+        <v>-0.7625490450300205</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.7512026265977241</v>
+        <v>-0.7550679376288301</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.9344223418574202</v>
+        <v>-0.9379041366182719</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.007738840904594</v>
+        <v>-1.014048867379501</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.250219591907886</v>
+        <v>-1.259123278642996</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.278422091339984</v>
+        <v>-1.287315923642069</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.552756119380717</v>
+        <v>-1.563859476319465</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.499692892130298</v>
+        <v>-1.514128182460404</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.420935654417598</v>
+        <v>-1.4385669406782</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3810</v>
+        <v>3821</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4537122638589608</v>
+        <v>-0.4496006094461862</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.376769836837326</v>
+        <v>-0.3755743261659745</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.705140977602106</v>
+        <v>-0.703102054933737</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.9273289930371149</v>
+        <v>-0.9246187120110392</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.8755611176510669</v>
+        <v>-0.877723590784079</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.6949970993307559</v>
+        <v>-0.6953092737391557</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.71318857811778</v>
+        <v>-0.7157672706956646</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.8778544216766946</v>
+        <v>-0.8800796508078292</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.8721861225062639</v>
+        <v>-0.8767438397464957</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.078597278845216</v>
+        <v>-1.085079525372379</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.11152250042425</v>
+        <v>-1.117965836665412</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-1.403704310686457</v>
+        <v>-1.411604730707872</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.415871206366873</v>
+        <v>-1.426151651123533</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-1.359365255222492</v>
+        <v>-1.372062068745826</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3885</v>
+        <v>3896</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3003105918478539</v>
+        <v>-0.2972696657670042</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1788355082530444</v>
+        <v>-0.1782428506774352</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4827667321725286</v>
+        <v>-0.4813959794939606</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6981117793989995</v>
+        <v>-0.6961085509472653</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.709010850577549</v>
+        <v>-0.710668566596695</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.5775279262424178</v>
+        <v>-0.5777048399315987</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.59697106146902</v>
+        <v>-0.5989051511300616</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.7160352582791418</v>
+        <v>-0.7177273124828076</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.711610394844854</v>
+        <v>-0.7151248465064484</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.9303904113719383</v>
+        <v>-0.9352554931954131</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.7865499406628089</v>
+        <v>-0.7918643580114022</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9694400170026896</v>
+        <v>-0.9760339026864457</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.015102675042549</v>
+        <v>-1.023454894088268</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.032446660587361</v>
+        <v>-1.042511014295314</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3947</v>
+        <v>3958</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.3344513840697019</v>
+        <v>-0.3318192033810661</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.08856587707128938</v>
+        <v>-0.08825112666751522</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2928361157306796</v>
+        <v>-0.2920155604890624</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.4521752790938933</v>
+        <v>-0.4508928571428612</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.5218337722589368</v>
+        <v>-0.5232258776007086</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.5141252030168673</v>
+        <v>-0.5141006799818584</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.5598665590748411</v>
+        <v>-0.561122593721997</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.6084878444784749</v>
+        <v>-0.6096816053730549</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.5544546024570138</v>
+        <v>-0.5572041984302345</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6565485771100086</v>
+        <v>-0.6605431619459736</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.568742470745633</v>
+        <v>-0.57301474976056</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.6721976426415992</v>
+        <v>-0.6775772997147058</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.7743245929136222</v>
+        <v>-0.7808864531213402</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.7117821544655456</v>
+        <v>-0.7198857695540752</v>
       </c>
     </row>
     <row r="34">
@@ -5364,101 +5364,101 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4020</v>
+        <v>4031</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1873380488829781</v>
+        <v>-0.1856805687049814</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.02464180613786482</v>
+        <v>-0.0245280888704329</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1579228757558511</v>
+        <v>-0.157487066591095</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2623555607946386</v>
+        <v>-0.2616219464771916</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.3404578980045088</v>
+        <v>-0.3414415030452744</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4019333023267535</v>
+        <v>-0.4017817701894515</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.498017977315321</v>
+        <v>-0.4985518206063162</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.5542112469664033</v>
+        <v>-0.5546407834301164</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4774057931427649</v>
+        <v>-0.4789906337598069</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4687925518844906</v>
+        <v>-0.4714293565068175</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3862475129554568</v>
+        <v>-0.3891321572500672</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.487155611845921</v>
+        <v>-0.4907036036666952</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5452712969827118</v>
+        <v>-0.5496472031905029</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.529459665063051</v>
+        <v>-0.5347992201251799</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 87.03</t>
+          <t>X &lt; 87.02</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4077</v>
+        <v>4088</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01147837772261795</v>
+        <v>-0.01072143229981037</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.05316566803792</v>
+        <v>0.05305255337179915</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.05928055336300986</v>
+        <v>-0.05911765219993725</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.160416409785654</v>
+        <v>-0.1599735062399859</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2693872570675993</v>
+        <v>-0.2698725936525079</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.2768784537089388</v>
+        <v>-0.2767314792758526</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.3238021613016215</v>
+        <v>-0.3241282583670042</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3367051249300985</v>
+        <v>-0.3370274246345346</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2617704177178553</v>
+        <v>-0.2628925165701972</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2405917980638748</v>
+        <v>-0.242421445522659</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2600430416068846</v>
+        <v>-0.2618348153092143</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3345138958804483</v>
+        <v>-0.3366990798633793</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.3240870020251094</v>
+        <v>-0.3269242181784549</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3052861983275577</v>
+        <v>-0.3087562876852559</v>
       </c>
     </row>
   </sheetData>
